--- a/datasertif.xlsx
+++ b/datasertif.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kantor\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A56752-A6A3-414E-A1C6-ED36A5129550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D9A6A10-5C5F-483B-A64E-01F48B4D525E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2A448DAF-C305-4C04-9E23-D5D3F33F0392}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12476" uniqueCount="10037">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12479" uniqueCount="10040">
   <si>
     <t>otp</t>
   </si>
@@ -30159,6 +30159,15 @@
   </si>
   <si>
     <t>18021997</t>
+  </si>
+  <si>
+    <t>06011981</t>
+  </si>
+  <si>
+    <t>14072001</t>
+  </si>
+  <si>
+    <t>29101984</t>
   </si>
 </sst>
 </file>
@@ -42379,9 +42388,8 @@
       <c r="A410" t="s">
         <v>6077</v>
       </c>
-      <c r="B410" s="3" t="str">
-        <f t="shared" ref="B410" si="0">LEFT(A410,2)&amp;MID(A410,4,2)&amp;RIGHT(A410,4)</f>
-        <v>81100333</v>
+      <c r="B410" s="3" t="s">
+        <v>10037</v>
       </c>
       <c r="C410" t="s">
         <v>6078</v>
@@ -47095,9 +47103,8 @@
       <c r="A582" t="s">
         <v>7139</v>
       </c>
-      <c r="B582" s="3" t="str">
-        <f t="shared" ref="B582" si="1">LEFT(A582,2)&amp;MID(A582,4,2)&amp;RIGHT(A582,4)</f>
-        <v>01700083</v>
+      <c r="B582" s="3" t="s">
+        <v>10038</v>
       </c>
       <c r="C582" t="s">
         <v>7140</v>
@@ -47487,9 +47494,8 @@
       <c r="A596" t="s">
         <v>7226</v>
       </c>
-      <c r="B596" s="3" t="str">
-        <f t="shared" ref="B596" si="2">LEFT(A596,2)&amp;MID(A596,4,2)&amp;RIGHT(A596,4)</f>
-        <v>84000552</v>
+      <c r="B596" s="3" t="s">
+        <v>10039</v>
       </c>
       <c r="C596" t="s">
         <v>7227</v>

--- a/datasertif.xlsx
+++ b/datasertif.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kantor\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D9A6A10-5C5F-483B-A64E-01F48B4D525E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2248B76-8B4B-47A0-AC78-0B544F74985E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2A448DAF-C305-4C04-9E23-D5D3F33F0392}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12479" uniqueCount="10040">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12478" uniqueCount="10039">
   <si>
     <t>otp</t>
   </si>
@@ -27015,9 +27015,6 @@
   </si>
   <si>
     <t>88120411</t>
-  </si>
-  <si>
-    <t>11048812</t>
   </si>
   <si>
     <t>Ruri Kurnia Putra</t>
@@ -42389,7 +42386,7 @@
         <v>6077</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>10037</v>
+        <v>10036</v>
       </c>
       <c r="C410" t="s">
         <v>6078</v>
@@ -45233,7 +45230,7 @@
         <v>6719</v>
       </c>
       <c r="B515" s="4" t="s">
-        <v>9486</v>
+        <v>9485</v>
       </c>
       <c r="C515" t="s">
         <v>6720</v>
@@ -46962,7 +46959,7 @@
         <v>7108</v>
       </c>
       <c r="B577" s="4" t="s">
-        <v>10036</v>
+        <v>10035</v>
       </c>
       <c r="C577" t="s">
         <v>7109</v>
@@ -47104,7 +47101,7 @@
         <v>7139</v>
       </c>
       <c r="B582" s="3" t="s">
-        <v>10038</v>
+        <v>10037</v>
       </c>
       <c r="C582" t="s">
         <v>7140</v>
@@ -47495,7 +47492,7 @@
         <v>7226</v>
       </c>
       <c r="B596" s="3" t="s">
-        <v>10039</v>
+        <v>10038</v>
       </c>
       <c r="C596" t="s">
         <v>7227</v>
@@ -55686,69 +55683,69 @@
       <c r="A897" t="s">
         <v>8988</v>
       </c>
-      <c r="B897" t="s">
+      <c r="B897">
+        <v>22121988</v>
+      </c>
+      <c r="C897" t="s">
         <v>8989</v>
       </c>
-      <c r="C897" t="s">
+      <c r="D897" t="s">
         <v>8990</v>
       </c>
-      <c r="D897" t="s">
+      <c r="E897" t="s">
         <v>8991</v>
       </c>
-      <c r="E897" t="s">
+      <c r="F897" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G897" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H897" t="s">
         <v>8992</v>
-      </c>
-      <c r="F897" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G897" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H897" t="s">
-        <v>8993</v>
       </c>
     </row>
     <row r="898" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A898" t="s">
+        <v>8993</v>
+      </c>
+      <c r="B898" t="s">
         <v>8994</v>
       </c>
-      <c r="B898" t="s">
+      <c r="C898" t="s">
         <v>8995</v>
       </c>
-      <c r="C898" t="s">
+      <c r="D898" t="s">
         <v>8996</v>
       </c>
-      <c r="D898" t="s">
+      <c r="E898" t="s">
         <v>8997</v>
       </c>
-      <c r="E898" t="s">
+      <c r="F898" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G898" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H898" t="s">
         <v>8998</v>
-      </c>
-      <c r="F898" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G898" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H898" t="s">
-        <v>8999</v>
       </c>
     </row>
     <row r="899" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A899" t="s">
+        <v>8999</v>
+      </c>
+      <c r="B899" t="s">
         <v>9000</v>
       </c>
-      <c r="B899" t="s">
+      <c r="C899" t="s">
         <v>9001</v>
       </c>
-      <c r="C899" t="s">
+      <c r="D899" t="s">
         <v>9002</v>
       </c>
-      <c r="D899" t="s">
+      <c r="E899" t="s">
         <v>9003</v>
-      </c>
-      <c r="E899" t="s">
-        <v>9004</v>
       </c>
       <c r="F899" t="s">
         <v>5496</v>
@@ -55760,24 +55757,24 @@
         <v>8121</v>
       </c>
       <c r="I899" t="s">
-        <v>9005</v>
+        <v>9004</v>
       </c>
     </row>
     <row r="900" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A900" t="s">
+        <v>9005</v>
+      </c>
+      <c r="B900" t="s">
         <v>9006</v>
       </c>
-      <c r="B900" t="s">
+      <c r="C900" t="s">
         <v>9007</v>
       </c>
-      <c r="C900" t="s">
+      <c r="D900" t="s">
         <v>9008</v>
       </c>
-      <c r="D900" t="s">
+      <c r="E900" t="s">
         <v>9009</v>
-      </c>
-      <c r="E900" t="s">
-        <v>9010</v>
       </c>
       <c r="F900" t="s">
         <v>5496</v>
@@ -55791,19 +55788,19 @@
     </row>
     <row r="901" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A901" t="s">
-        <v>9011</v>
+        <v>9010</v>
       </c>
       <c r="B901" t="s">
         <v>6505</v>
       </c>
       <c r="C901" t="s">
+        <v>9011</v>
+      </c>
+      <c r="D901" t="s">
         <v>9012</v>
       </c>
-      <c r="D901" t="s">
+      <c r="E901" t="s">
         <v>9013</v>
-      </c>
-      <c r="E901" t="s">
-        <v>9014</v>
       </c>
       <c r="F901" t="s">
         <v>5496</v>
@@ -55815,33 +55812,33 @@
         <v>7205</v>
       </c>
       <c r="I901" t="s">
-        <v>9015</v>
+        <v>9014</v>
       </c>
     </row>
     <row r="902" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A902" t="s">
+        <v>9015</v>
+      </c>
+      <c r="B902" t="s">
         <v>9016</v>
       </c>
-      <c r="B902" t="s">
+      <c r="C902" t="s">
         <v>9017</v>
       </c>
-      <c r="C902" t="s">
+      <c r="D902" t="s">
         <v>9018</v>
       </c>
-      <c r="D902" t="s">
+      <c r="E902" t="s">
         <v>9019</v>
       </c>
-      <c r="E902" t="s">
+      <c r="F902" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G902" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H902" t="s">
         <v>9020</v>
-      </c>
-      <c r="F902" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G902" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H902" t="s">
-        <v>9021</v>
       </c>
     </row>
     <row r="903" spans="1:9" x14ac:dyDescent="0.3">
@@ -55849,16 +55846,16 @@
         <v>224</v>
       </c>
       <c r="B903" t="s">
+        <v>9021</v>
+      </c>
+      <c r="C903" t="s">
         <v>9022</v>
       </c>
-      <c r="C903" t="s">
+      <c r="D903" t="s">
         <v>9023</v>
       </c>
-      <c r="D903" t="s">
+      <c r="E903" t="s">
         <v>9024</v>
-      </c>
-      <c r="E903" t="s">
-        <v>9025</v>
       </c>
       <c r="F903" t="s">
         <v>5496</v>
@@ -55870,82 +55867,82 @@
         <v>6147</v>
       </c>
       <c r="I903" t="s">
-        <v>9026</v>
+        <v>9025</v>
       </c>
     </row>
     <row r="904" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A904" t="s">
+        <v>9026</v>
+      </c>
+      <c r="B904" t="s">
         <v>9027</v>
       </c>
-      <c r="B904" t="s">
+      <c r="C904" t="s">
         <v>9028</v>
       </c>
-      <c r="C904" t="s">
+      <c r="D904" t="s">
         <v>9029</v>
       </c>
-      <c r="D904" t="s">
+      <c r="E904" t="s">
         <v>9030</v>
       </c>
-      <c r="E904" t="s">
+      <c r="F904" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G904" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H904" t="s">
         <v>9031</v>
       </c>
-      <c r="F904" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G904" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H904" t="s">
+      <c r="I904" t="s">
         <v>9032</v>
-      </c>
-      <c r="I904" t="s">
-        <v>9033</v>
       </c>
     </row>
     <row r="905" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A905" t="s">
+        <v>9033</v>
+      </c>
+      <c r="B905" t="s">
         <v>9034</v>
       </c>
-      <c r="B905" t="s">
+      <c r="C905" t="s">
         <v>9035</v>
       </c>
-      <c r="C905" t="s">
+      <c r="D905" t="s">
         <v>9036</v>
       </c>
-      <c r="D905" t="s">
+      <c r="E905" t="s">
         <v>9037</v>
       </c>
-      <c r="E905" t="s">
+      <c r="F905" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G905" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H905" t="s">
         <v>9038</v>
       </c>
-      <c r="F905" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G905" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H905" t="s">
+      <c r="I905" t="s">
         <v>9039</v>
-      </c>
-      <c r="I905" t="s">
-        <v>9040</v>
       </c>
     </row>
     <row r="906" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A906" t="s">
+        <v>9040</v>
+      </c>
+      <c r="B906" t="s">
         <v>9041</v>
       </c>
-      <c r="B906" t="s">
+      <c r="C906" t="s">
         <v>9042</v>
       </c>
-      <c r="C906" t="s">
+      <c r="D906" t="s">
         <v>9043</v>
       </c>
-      <c r="D906" t="s">
+      <c r="E906" t="s">
         <v>9044</v>
-      </c>
-      <c r="E906" t="s">
-        <v>9045</v>
       </c>
       <c r="F906" t="s">
         <v>5496</v>
@@ -55959,19 +55956,19 @@
     </row>
     <row r="907" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A907" t="s">
+        <v>9045</v>
+      </c>
+      <c r="B907" t="s">
         <v>9046</v>
       </c>
-      <c r="B907" t="s">
+      <c r="C907" t="s">
         <v>9047</v>
       </c>
-      <c r="C907" t="s">
+      <c r="D907" t="s">
         <v>9048</v>
       </c>
-      <c r="D907" t="s">
+      <c r="E907" t="s">
         <v>9049</v>
-      </c>
-      <c r="E907" t="s">
-        <v>9050</v>
       </c>
       <c r="F907" t="s">
         <v>5496</v>
@@ -55985,19 +55982,19 @@
     </row>
     <row r="908" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A908" t="s">
+        <v>9050</v>
+      </c>
+      <c r="B908" t="s">
         <v>9051</v>
       </c>
-      <c r="B908" t="s">
+      <c r="C908" t="s">
         <v>9052</v>
       </c>
-      <c r="C908" t="s">
+      <c r="D908" t="s">
         <v>9053</v>
       </c>
-      <c r="D908" t="s">
+      <c r="E908" t="s">
         <v>9054</v>
-      </c>
-      <c r="E908" t="s">
-        <v>9055</v>
       </c>
       <c r="F908" t="s">
         <v>5496</v>
@@ -56009,50 +56006,50 @@
         <v>8264</v>
       </c>
       <c r="I908" t="s">
-        <v>9056</v>
+        <v>9055</v>
       </c>
     </row>
     <row r="909" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A909" t="s">
+        <v>9056</v>
+      </c>
+      <c r="B909" t="s">
         <v>9057</v>
       </c>
-      <c r="B909" t="s">
+      <c r="C909" t="s">
         <v>9058</v>
       </c>
-      <c r="C909" t="s">
+      <c r="D909" t="s">
         <v>9059</v>
       </c>
-      <c r="D909" t="s">
+      <c r="E909" t="s">
         <v>9060</v>
       </c>
-      <c r="E909" t="s">
+      <c r="F909" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G909" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H909" t="s">
         <v>9061</v>
-      </c>
-      <c r="F909" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G909" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H909" t="s">
-        <v>9062</v>
       </c>
     </row>
     <row r="910" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A910" t="s">
+        <v>9062</v>
+      </c>
+      <c r="B910" t="s">
         <v>9063</v>
       </c>
-      <c r="B910" t="s">
+      <c r="C910" t="s">
         <v>9064</v>
       </c>
-      <c r="C910" t="s">
+      <c r="D910" t="s">
         <v>9065</v>
       </c>
-      <c r="D910" t="s">
+      <c r="E910" t="s">
         <v>9066</v>
-      </c>
-      <c r="E910" t="s">
-        <v>9067</v>
       </c>
       <c r="F910" t="s">
         <v>5496</v>
@@ -56066,19 +56063,19 @@
     </row>
     <row r="911" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A911" t="s">
+        <v>9067</v>
+      </c>
+      <c r="B911" t="s">
         <v>9068</v>
       </c>
-      <c r="B911" t="s">
+      <c r="C911" t="s">
         <v>9069</v>
       </c>
-      <c r="C911" t="s">
+      <c r="D911" t="s">
         <v>9070</v>
       </c>
-      <c r="D911" t="s">
+      <c r="E911" t="s">
         <v>9071</v>
-      </c>
-      <c r="E911" t="s">
-        <v>9072</v>
       </c>
       <c r="F911" t="s">
         <v>5496</v>
@@ -56090,50 +56087,50 @@
         <v>6075</v>
       </c>
       <c r="I911" t="s">
-        <v>9073</v>
+        <v>9072</v>
       </c>
     </row>
     <row r="912" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A912" t="s">
+        <v>9073</v>
+      </c>
+      <c r="B912" t="s">
         <v>9074</v>
       </c>
-      <c r="B912" t="s">
+      <c r="C912" t="s">
         <v>9075</v>
       </c>
-      <c r="C912" t="s">
+      <c r="D912" t="s">
         <v>9076</v>
       </c>
-      <c r="D912" t="s">
+      <c r="E912" t="s">
         <v>9077</v>
       </c>
-      <c r="E912" t="s">
+      <c r="F912" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G912" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H912" t="s">
         <v>9078</v>
-      </c>
-      <c r="F912" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G912" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H912" t="s">
-        <v>9079</v>
       </c>
     </row>
     <row r="913" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A913" t="s">
+        <v>9079</v>
+      </c>
+      <c r="B913" t="s">
         <v>9080</v>
       </c>
-      <c r="B913" t="s">
+      <c r="C913" t="s">
         <v>9081</v>
       </c>
-      <c r="C913" t="s">
+      <c r="D913" t="s">
         <v>9082</v>
       </c>
-      <c r="D913" t="s">
+      <c r="E913" t="s">
         <v>9083</v>
-      </c>
-      <c r="E913" t="s">
-        <v>9084</v>
       </c>
       <c r="F913" t="s">
         <v>5496</v>
@@ -56145,24 +56142,24 @@
         <v>7008</v>
       </c>
       <c r="I913" t="s">
-        <v>9085</v>
+        <v>9084</v>
       </c>
     </row>
     <row r="914" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A914" t="s">
+        <v>9085</v>
+      </c>
+      <c r="B914" t="s">
         <v>9086</v>
       </c>
-      <c r="B914" t="s">
+      <c r="C914" t="s">
         <v>9087</v>
       </c>
-      <c r="C914" t="s">
+      <c r="D914" t="s">
         <v>9088</v>
       </c>
-      <c r="D914" t="s">
+      <c r="E914" t="s">
         <v>9089</v>
-      </c>
-      <c r="E914" t="s">
-        <v>9090</v>
       </c>
       <c r="F914" t="s">
         <v>5496</v>
@@ -56176,45 +56173,45 @@
     </row>
     <row r="915" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A915" t="s">
+        <v>9090</v>
+      </c>
+      <c r="B915" t="s">
         <v>9091</v>
       </c>
-      <c r="B915" t="s">
+      <c r="C915" t="s">
         <v>9092</v>
       </c>
-      <c r="C915" t="s">
+      <c r="D915" t="s">
         <v>9093</v>
       </c>
-      <c r="D915" t="s">
+      <c r="E915" t="s">
         <v>9094</v>
       </c>
-      <c r="E915" t="s">
+      <c r="F915" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G915" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H915" t="s">
         <v>9095</v>
-      </c>
-      <c r="F915" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G915" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H915" t="s">
-        <v>9096</v>
       </c>
     </row>
     <row r="916" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A916" t="s">
+        <v>9096</v>
+      </c>
+      <c r="B916" t="s">
         <v>9097</v>
       </c>
-      <c r="B916" t="s">
+      <c r="C916" t="s">
         <v>9098</v>
       </c>
-      <c r="C916" t="s">
+      <c r="D916" t="s">
         <v>9099</v>
       </c>
-      <c r="D916" t="s">
+      <c r="E916" t="s">
         <v>9100</v>
-      </c>
-      <c r="E916" t="s">
-        <v>9101</v>
       </c>
       <c r="F916" t="s">
         <v>5496</v>
@@ -56226,50 +56223,50 @@
         <v>8824</v>
       </c>
       <c r="I916" t="s">
-        <v>9102</v>
+        <v>9101</v>
       </c>
     </row>
     <row r="917" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A917" t="s">
+        <v>9102</v>
+      </c>
+      <c r="B917" t="s">
         <v>9103</v>
       </c>
-      <c r="B917" t="s">
+      <c r="C917" t="s">
         <v>9104</v>
       </c>
-      <c r="C917" t="s">
+      <c r="D917" t="s">
         <v>9105</v>
       </c>
-      <c r="D917" t="s">
+      <c r="E917" t="s">
         <v>9106</v>
       </c>
-      <c r="E917" t="s">
+      <c r="F917" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G917" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H917" t="s">
         <v>9107</v>
-      </c>
-      <c r="F917" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G917" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H917" t="s">
-        <v>9108</v>
       </c>
     </row>
     <row r="918" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A918" t="s">
+        <v>9108</v>
+      </c>
+      <c r="B918" t="s">
         <v>9109</v>
       </c>
-      <c r="B918" t="s">
+      <c r="C918" t="s">
         <v>9110</v>
       </c>
-      <c r="C918" t="s">
+      <c r="D918" t="s">
         <v>9111</v>
       </c>
-      <c r="D918" t="s">
+      <c r="E918" t="s">
         <v>9112</v>
-      </c>
-      <c r="E918" t="s">
-        <v>9113</v>
       </c>
       <c r="F918" t="s">
         <v>5496</v>
@@ -56283,19 +56280,19 @@
     </row>
     <row r="919" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A919" t="s">
+        <v>9113</v>
+      </c>
+      <c r="B919" t="s">
         <v>9114</v>
       </c>
-      <c r="B919" t="s">
+      <c r="C919" t="s">
         <v>9115</v>
       </c>
-      <c r="C919" t="s">
+      <c r="D919" t="s">
         <v>9116</v>
       </c>
-      <c r="D919" t="s">
+      <c r="E919" t="s">
         <v>9117</v>
-      </c>
-      <c r="E919" t="s">
-        <v>9118</v>
       </c>
       <c r="F919" t="s">
         <v>5496</v>
@@ -56307,24 +56304,24 @@
         <v>7266</v>
       </c>
       <c r="I919" t="s">
-        <v>9119</v>
+        <v>9118</v>
       </c>
     </row>
     <row r="920" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A920" t="s">
+        <v>9119</v>
+      </c>
+      <c r="B920" t="s">
         <v>9120</v>
       </c>
-      <c r="B920" t="s">
+      <c r="C920" t="s">
         <v>9121</v>
       </c>
-      <c r="C920" t="s">
+      <c r="D920" t="s">
         <v>9122</v>
       </c>
-      <c r="D920" t="s">
+      <c r="E920" t="s">
         <v>9123</v>
-      </c>
-      <c r="E920" t="s">
-        <v>9124</v>
       </c>
       <c r="F920" t="s">
         <v>5496</v>
@@ -56338,19 +56335,19 @@
     </row>
     <row r="921" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A921" t="s">
+        <v>9124</v>
+      </c>
+      <c r="B921" t="s">
         <v>9125</v>
       </c>
-      <c r="B921" t="s">
+      <c r="C921" t="s">
         <v>9126</v>
       </c>
-      <c r="C921" t="s">
+      <c r="D921" t="s">
         <v>9127</v>
       </c>
-      <c r="D921" t="s">
+      <c r="E921" t="s">
         <v>9128</v>
-      </c>
-      <c r="E921" t="s">
-        <v>9129</v>
       </c>
       <c r="F921" t="s">
         <v>5496</v>
@@ -56362,24 +56359,24 @@
         <v>5503</v>
       </c>
       <c r="I921" t="s">
-        <v>9130</v>
+        <v>9129</v>
       </c>
     </row>
     <row r="922" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A922" t="s">
+        <v>9130</v>
+      </c>
+      <c r="B922" t="s">
         <v>9131</v>
       </c>
-      <c r="B922" t="s">
+      <c r="C922" t="s">
         <v>9132</v>
       </c>
-      <c r="C922" t="s">
+      <c r="D922" t="s">
         <v>9133</v>
       </c>
-      <c r="D922" t="s">
+      <c r="E922" t="s">
         <v>9134</v>
-      </c>
-      <c r="E922" t="s">
-        <v>9135</v>
       </c>
       <c r="F922" t="s">
         <v>5496</v>
@@ -56393,100 +56390,100 @@
     </row>
     <row r="923" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A923" t="s">
+        <v>9135</v>
+      </c>
+      <c r="B923" t="s">
         <v>9136</v>
       </c>
-      <c r="B923" t="s">
+      <c r="C923" t="s">
         <v>9137</v>
       </c>
-      <c r="C923" t="s">
+      <c r="D923" t="s">
         <v>9138</v>
       </c>
-      <c r="D923" t="s">
+      <c r="E923" t="s">
         <v>9139</v>
       </c>
-      <c r="E923" t="s">
+      <c r="F923" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G923" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H923" t="s">
         <v>9140</v>
-      </c>
-      <c r="F923" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G923" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H923" t="s">
-        <v>9141</v>
       </c>
     </row>
     <row r="924" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A924" t="s">
+        <v>9141</v>
+      </c>
+      <c r="B924" t="s">
         <v>9142</v>
       </c>
-      <c r="B924" t="s">
+      <c r="C924" t="s">
         <v>9143</v>
       </c>
-      <c r="C924" t="s">
+      <c r="D924" t="s">
         <v>9144</v>
       </c>
-      <c r="D924" t="s">
+      <c r="E924" t="s">
         <v>9145</v>
       </c>
-      <c r="E924" t="s">
+      <c r="F924" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G924" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H924" t="s">
         <v>9146</v>
       </c>
-      <c r="F924" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G924" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H924" t="s">
+      <c r="I924" t="s">
         <v>9147</v>
-      </c>
-      <c r="I924" t="s">
-        <v>9148</v>
       </c>
     </row>
     <row r="925" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A925" t="s">
+        <v>9148</v>
+      </c>
+      <c r="B925" t="s">
         <v>9149</v>
       </c>
-      <c r="B925" t="s">
+      <c r="C925" t="s">
         <v>9150</v>
       </c>
-      <c r="C925" t="s">
+      <c r="D925" t="s">
         <v>9151</v>
       </c>
-      <c r="D925" t="s">
+      <c r="E925" t="s">
         <v>9152</v>
       </c>
-      <c r="E925" t="s">
+      <c r="F925" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G925" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H925" t="s">
         <v>9153</v>
-      </c>
-      <c r="F925" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G925" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H925" t="s">
-        <v>9154</v>
       </c>
     </row>
     <row r="926" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A926" t="s">
+        <v>9154</v>
+      </c>
+      <c r="B926" t="s">
         <v>9155</v>
       </c>
-      <c r="B926" t="s">
+      <c r="C926" t="s">
         <v>9156</v>
       </c>
-      <c r="C926" t="s">
+      <c r="D926" t="s">
         <v>9157</v>
       </c>
-      <c r="D926" t="s">
+      <c r="E926" t="s">
         <v>9158</v>
-      </c>
-      <c r="E926" t="s">
-        <v>9159</v>
       </c>
       <c r="F926" t="s">
         <v>5496</v>
@@ -56500,19 +56497,19 @@
     </row>
     <row r="927" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A927" t="s">
+        <v>9159</v>
+      </c>
+      <c r="B927" t="s">
         <v>9160</v>
       </c>
-      <c r="B927" t="s">
+      <c r="C927" t="s">
         <v>9161</v>
       </c>
-      <c r="C927" t="s">
+      <c r="D927" t="s">
         <v>9162</v>
       </c>
-      <c r="D927" t="s">
+      <c r="E927" t="s">
         <v>9163</v>
-      </c>
-      <c r="E927" t="s">
-        <v>9164</v>
       </c>
       <c r="F927" t="s">
         <v>5496</v>
@@ -56526,45 +56523,45 @@
     </row>
     <row r="928" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A928" t="s">
+        <v>9164</v>
+      </c>
+      <c r="B928" t="s">
         <v>9165</v>
       </c>
-      <c r="B928" t="s">
+      <c r="C928" t="s">
         <v>9166</v>
       </c>
-      <c r="C928" t="s">
+      <c r="D928" t="s">
         <v>9167</v>
       </c>
-      <c r="D928" t="s">
+      <c r="E928" t="s">
         <v>9168</v>
       </c>
-      <c r="E928" t="s">
+      <c r="F928" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G928" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H928" t="s">
         <v>9169</v>
-      </c>
-      <c r="F928" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G928" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H928" t="s">
-        <v>9170</v>
       </c>
     </row>
     <row r="929" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A929" t="s">
+        <v>9170</v>
+      </c>
+      <c r="B929" t="s">
         <v>9171</v>
       </c>
-      <c r="B929" t="s">
+      <c r="C929" t="s">
         <v>9172</v>
       </c>
-      <c r="C929" t="s">
+      <c r="D929" t="s">
         <v>9173</v>
       </c>
-      <c r="D929" t="s">
+      <c r="E929" t="s">
         <v>9174</v>
-      </c>
-      <c r="E929" t="s">
-        <v>9175</v>
       </c>
       <c r="F929" t="s">
         <v>5496</v>
@@ -56578,71 +56575,71 @@
     </row>
     <row r="930" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A930" t="s">
+        <v>9175</v>
+      </c>
+      <c r="B930" t="s">
         <v>9176</v>
       </c>
-      <c r="B930" t="s">
+      <c r="C930" t="s">
         <v>9177</v>
       </c>
-      <c r="C930" t="s">
+      <c r="D930" t="s">
         <v>9178</v>
       </c>
-      <c r="D930" t="s">
+      <c r="E930" t="s">
         <v>9179</v>
       </c>
-      <c r="E930" t="s">
+      <c r="F930" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G930" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H930" t="s">
         <v>9180</v>
-      </c>
-      <c r="F930" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G930" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H930" t="s">
-        <v>9181</v>
       </c>
     </row>
     <row r="931" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A931" t="s">
+        <v>9181</v>
+      </c>
+      <c r="B931" t="s">
         <v>9182</v>
       </c>
-      <c r="B931" t="s">
+      <c r="C931" t="s">
         <v>9183</v>
       </c>
-      <c r="C931" t="s">
+      <c r="D931" t="s">
         <v>9184</v>
       </c>
-      <c r="D931" t="s">
+      <c r="E931" t="s">
         <v>9185</v>
       </c>
-      <c r="E931" t="s">
+      <c r="F931" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G931" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H931" t="s">
         <v>9186</v>
-      </c>
-      <c r="F931" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G931" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H931" t="s">
-        <v>9187</v>
       </c>
     </row>
     <row r="932" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A932" t="s">
+        <v>9187</v>
+      </c>
+      <c r="B932" t="s">
         <v>9188</v>
       </c>
-      <c r="B932" t="s">
+      <c r="C932" t="s">
         <v>9189</v>
       </c>
-      <c r="C932" t="s">
+      <c r="D932" t="s">
         <v>9190</v>
       </c>
-      <c r="D932" t="s">
+      <c r="E932" t="s">
         <v>9191</v>
-      </c>
-      <c r="E932" t="s">
-        <v>9192</v>
       </c>
       <c r="F932" t="s">
         <v>5496</v>
@@ -56656,19 +56653,19 @@
     </row>
     <row r="933" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A933" t="s">
+        <v>9192</v>
+      </c>
+      <c r="B933" t="s">
         <v>9193</v>
       </c>
-      <c r="B933" t="s">
+      <c r="C933" t="s">
         <v>9194</v>
       </c>
-      <c r="C933" t="s">
+      <c r="D933" t="s">
         <v>9195</v>
       </c>
-      <c r="D933" t="s">
+      <c r="E933" t="s">
         <v>9196</v>
-      </c>
-      <c r="E933" t="s">
-        <v>9197</v>
       </c>
       <c r="F933" t="s">
         <v>5496</v>
@@ -56682,100 +56679,100 @@
     </row>
     <row r="934" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A934" t="s">
+        <v>9197</v>
+      </c>
+      <c r="B934" t="s">
         <v>9198</v>
       </c>
-      <c r="B934" t="s">
+      <c r="C934" t="s">
         <v>9199</v>
       </c>
-      <c r="C934" t="s">
+      <c r="D934" t="s">
         <v>9200</v>
       </c>
-      <c r="D934" t="s">
+      <c r="E934" t="s">
         <v>9201</v>
       </c>
-      <c r="E934" t="s">
+      <c r="F934" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G934" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H934" t="s">
         <v>9202</v>
       </c>
-      <c r="F934" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G934" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H934" t="s">
+      <c r="I934" t="s">
         <v>9203</v>
-      </c>
-      <c r="I934" t="s">
-        <v>9204</v>
       </c>
     </row>
     <row r="935" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A935" t="s">
+        <v>9204</v>
+      </c>
+      <c r="B935" t="s">
         <v>9205</v>
       </c>
-      <c r="B935" t="s">
+      <c r="C935" t="s">
         <v>9206</v>
       </c>
-      <c r="C935" t="s">
+      <c r="D935" t="s">
         <v>9207</v>
       </c>
-      <c r="D935" t="s">
+      <c r="E935" t="s">
         <v>9208</v>
       </c>
-      <c r="E935" t="s">
+      <c r="F935" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G935" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H935" t="s">
         <v>9209</v>
-      </c>
-      <c r="F935" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G935" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H935" t="s">
-        <v>9210</v>
       </c>
     </row>
     <row r="936" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A936" t="s">
+        <v>9210</v>
+      </c>
+      <c r="B936" t="s">
         <v>9211</v>
       </c>
-      <c r="B936" t="s">
+      <c r="C936" t="s">
         <v>9212</v>
       </c>
-      <c r="C936" t="s">
+      <c r="D936" t="s">
         <v>9213</v>
       </c>
-      <c r="D936" t="s">
+      <c r="E936" t="s">
         <v>9214</v>
       </c>
-      <c r="E936" t="s">
+      <c r="F936" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G936" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H936" t="s">
         <v>9215</v>
-      </c>
-      <c r="F936" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G936" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H936" t="s">
-        <v>9216</v>
       </c>
     </row>
     <row r="937" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A937" t="s">
+        <v>9216</v>
+      </c>
+      <c r="B937" t="s">
         <v>9217</v>
       </c>
-      <c r="B937" t="s">
+      <c r="C937" t="s">
         <v>9218</v>
       </c>
-      <c r="C937" t="s">
+      <c r="D937" t="s">
         <v>9219</v>
       </c>
-      <c r="D937" t="s">
+      <c r="E937" t="s">
         <v>9220</v>
-      </c>
-      <c r="E937" t="s">
-        <v>9221</v>
       </c>
       <c r="F937" t="s">
         <v>5496</v>
@@ -56789,45 +56786,45 @@
     </row>
     <row r="938" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A938" t="s">
+        <v>9221</v>
+      </c>
+      <c r="B938" t="s">
         <v>9222</v>
       </c>
-      <c r="B938" t="s">
+      <c r="C938" t="s">
         <v>9223</v>
       </c>
-      <c r="C938" t="s">
+      <c r="D938" t="s">
         <v>9224</v>
       </c>
-      <c r="D938" t="s">
+      <c r="E938" t="s">
         <v>9225</v>
       </c>
-      <c r="E938" t="s">
+      <c r="F938" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G938" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H938" t="s">
         <v>9226</v>
-      </c>
-      <c r="F938" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G938" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H938" t="s">
-        <v>9227</v>
       </c>
     </row>
     <row r="939" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A939" t="s">
+        <v>9227</v>
+      </c>
+      <c r="B939" t="s">
         <v>9228</v>
       </c>
-      <c r="B939" t="s">
+      <c r="C939" t="s">
         <v>9229</v>
       </c>
-      <c r="C939" t="s">
+      <c r="D939" t="s">
         <v>9230</v>
       </c>
-      <c r="D939" t="s">
+      <c r="E939" t="s">
         <v>9231</v>
-      </c>
-      <c r="E939" t="s">
-        <v>9232</v>
       </c>
       <c r="F939" t="s">
         <v>5496</v>
@@ -56839,24 +56836,24 @@
         <v>8562</v>
       </c>
       <c r="I939" t="s">
-        <v>9233</v>
+        <v>9232</v>
       </c>
     </row>
     <row r="940" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A940" t="s">
+        <v>9233</v>
+      </c>
+      <c r="B940" t="s">
         <v>9234</v>
       </c>
-      <c r="B940" t="s">
+      <c r="C940" t="s">
         <v>9235</v>
       </c>
-      <c r="C940" t="s">
+      <c r="D940" t="s">
         <v>9236</v>
       </c>
-      <c r="D940" t="s">
+      <c r="E940" t="s">
         <v>9237</v>
-      </c>
-      <c r="E940" t="s">
-        <v>9238</v>
       </c>
       <c r="F940" t="s">
         <v>5496</v>
@@ -56870,45 +56867,45 @@
     </row>
     <row r="941" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A941" t="s">
+        <v>9238</v>
+      </c>
+      <c r="B941" t="s">
         <v>9239</v>
       </c>
-      <c r="B941" t="s">
+      <c r="C941" t="s">
         <v>9240</v>
       </c>
-      <c r="C941" t="s">
+      <c r="D941" t="s">
         <v>9241</v>
       </c>
-      <c r="D941" t="s">
+      <c r="E941" t="s">
         <v>9242</v>
       </c>
-      <c r="E941" t="s">
+      <c r="F941" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G941" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H941" t="s">
         <v>9243</v>
-      </c>
-      <c r="F941" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G941" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H941" t="s">
-        <v>9244</v>
       </c>
     </row>
     <row r="942" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A942" t="s">
+        <v>9244</v>
+      </c>
+      <c r="B942" t="s">
         <v>9245</v>
       </c>
-      <c r="B942" t="s">
+      <c r="C942" t="s">
         <v>9246</v>
       </c>
-      <c r="C942" t="s">
+      <c r="D942" t="s">
         <v>9247</v>
       </c>
-      <c r="D942" t="s">
+      <c r="E942" t="s">
         <v>9248</v>
-      </c>
-      <c r="E942" t="s">
-        <v>9249</v>
       </c>
       <c r="F942" t="s">
         <v>5496</v>
@@ -56922,45 +56919,45 @@
     </row>
     <row r="943" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A943" t="s">
+        <v>9249</v>
+      </c>
+      <c r="B943" t="s">
         <v>9250</v>
       </c>
-      <c r="B943" t="s">
+      <c r="C943" t="s">
         <v>9251</v>
       </c>
-      <c r="C943" t="s">
+      <c r="D943" t="s">
         <v>9252</v>
       </c>
-      <c r="D943" t="s">
+      <c r="E943" t="s">
         <v>9253</v>
       </c>
-      <c r="E943" t="s">
+      <c r="F943" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G943" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H943" t="s">
         <v>9254</v>
-      </c>
-      <c r="F943" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G943" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H943" t="s">
-        <v>9255</v>
       </c>
     </row>
     <row r="944" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A944" t="s">
+        <v>9255</v>
+      </c>
+      <c r="B944" t="s">
         <v>9256</v>
       </c>
-      <c r="B944" t="s">
+      <c r="C944" t="s">
         <v>9257</v>
       </c>
-      <c r="C944" t="s">
+      <c r="D944" t="s">
         <v>9258</v>
       </c>
-      <c r="D944" t="s">
+      <c r="E944" t="s">
         <v>9259</v>
-      </c>
-      <c r="E944" t="s">
-        <v>9260</v>
       </c>
       <c r="F944" t="s">
         <v>5496</v>
@@ -56974,19 +56971,19 @@
     </row>
     <row r="945" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A945" t="s">
-        <v>9261</v>
+        <v>9260</v>
       </c>
       <c r="B945" t="s">
         <v>7114</v>
       </c>
       <c r="C945" t="s">
+        <v>9261</v>
+      </c>
+      <c r="D945" t="s">
         <v>9262</v>
       </c>
-      <c r="D945" t="s">
+      <c r="E945" t="s">
         <v>9263</v>
-      </c>
-      <c r="E945" t="s">
-        <v>9264</v>
       </c>
       <c r="F945" t="s">
         <v>5496</v>
@@ -56998,76 +56995,76 @@
         <v>6484</v>
       </c>
       <c r="I945" t="s">
-        <v>9265</v>
+        <v>9264</v>
       </c>
     </row>
     <row r="946" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A946" t="s">
+        <v>9265</v>
+      </c>
+      <c r="B946" t="s">
         <v>9266</v>
       </c>
-      <c r="B946" t="s">
+      <c r="C946" t="s">
         <v>9267</v>
       </c>
-      <c r="C946" t="s">
+      <c r="D946" t="s">
         <v>9268</v>
       </c>
-      <c r="D946" t="s">
+      <c r="E946" t="s">
         <v>9269</v>
       </c>
-      <c r="E946" t="s">
+      <c r="F946" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G946" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H946" t="s">
         <v>9270</v>
-      </c>
-      <c r="F946" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G946" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H946" t="s">
-        <v>9271</v>
       </c>
     </row>
     <row r="947" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A947" t="s">
+        <v>9271</v>
+      </c>
+      <c r="B947" t="s">
         <v>9272</v>
       </c>
-      <c r="B947" t="s">
+      <c r="C947" t="s">
         <v>9273</v>
       </c>
-      <c r="C947" t="s">
+      <c r="D947" t="s">
         <v>9274</v>
       </c>
-      <c r="D947" t="s">
+      <c r="E947" t="s">
         <v>9275</v>
       </c>
-      <c r="E947" t="s">
+      <c r="F947" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G947" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H947" t="s">
         <v>9276</v>
-      </c>
-      <c r="F947" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G947" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H947" t="s">
-        <v>9277</v>
       </c>
     </row>
     <row r="948" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A948" t="s">
+        <v>9277</v>
+      </c>
+      <c r="B948" t="s">
         <v>9278</v>
       </c>
-      <c r="B948" t="s">
+      <c r="C948" t="s">
         <v>9279</v>
       </c>
-      <c r="C948" t="s">
+      <c r="D948" t="s">
         <v>9280</v>
       </c>
-      <c r="D948" t="s">
+      <c r="E948" t="s">
         <v>9281</v>
-      </c>
-      <c r="E948" t="s">
-        <v>9282</v>
       </c>
       <c r="F948" t="s">
         <v>5496</v>
@@ -57081,45 +57078,45 @@
     </row>
     <row r="949" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A949" t="s">
+        <v>9282</v>
+      </c>
+      <c r="B949" t="s">
         <v>9283</v>
       </c>
-      <c r="B949" t="s">
+      <c r="C949" t="s">
         <v>9284</v>
       </c>
-      <c r="C949" t="s">
+      <c r="D949" t="s">
         <v>9285</v>
       </c>
-      <c r="D949" t="s">
+      <c r="E949" t="s">
         <v>9286</v>
       </c>
-      <c r="E949" t="s">
+      <c r="F949" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G949" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H949" t="s">
         <v>9287</v>
-      </c>
-      <c r="F949" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G949" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H949" t="s">
-        <v>9288</v>
       </c>
     </row>
     <row r="950" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A950" t="s">
+        <v>9288</v>
+      </c>
+      <c r="B950" t="s">
         <v>9289</v>
       </c>
-      <c r="B950" t="s">
+      <c r="C950" t="s">
         <v>9290</v>
       </c>
-      <c r="C950" t="s">
+      <c r="D950" t="s">
         <v>9291</v>
       </c>
-      <c r="D950" t="s">
+      <c r="E950" t="s">
         <v>9292</v>
-      </c>
-      <c r="E950" t="s">
-        <v>9293</v>
       </c>
       <c r="F950" t="s">
         <v>5496</v>
@@ -57133,19 +57130,19 @@
     </row>
     <row r="951" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A951" t="s">
+        <v>9293</v>
+      </c>
+      <c r="B951" t="s">
         <v>9294</v>
       </c>
-      <c r="B951" t="s">
+      <c r="C951" t="s">
         <v>9295</v>
       </c>
-      <c r="C951" t="s">
+      <c r="D951" t="s">
         <v>9296</v>
       </c>
-      <c r="D951" t="s">
+      <c r="E951" t="s">
         <v>9297</v>
-      </c>
-      <c r="E951" t="s">
-        <v>9298</v>
       </c>
       <c r="F951" t="s">
         <v>5496</v>
@@ -57159,45 +57156,45 @@
     </row>
     <row r="952" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A952" t="s">
+        <v>9298</v>
+      </c>
+      <c r="B952" t="s">
         <v>9299</v>
       </c>
-      <c r="B952" t="s">
+      <c r="C952" t="s">
         <v>9300</v>
       </c>
-      <c r="C952" t="s">
+      <c r="D952" t="s">
         <v>9301</v>
       </c>
-      <c r="D952" t="s">
+      <c r="E952" t="s">
         <v>9302</v>
       </c>
-      <c r="E952" t="s">
+      <c r="F952" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G952" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H952" t="s">
         <v>9303</v>
-      </c>
-      <c r="F952" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G952" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H952" t="s">
-        <v>9304</v>
       </c>
     </row>
     <row r="953" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A953" t="s">
+        <v>9304</v>
+      </c>
+      <c r="B953" t="s">
         <v>9305</v>
       </c>
-      <c r="B953" t="s">
+      <c r="C953" t="s">
         <v>9306</v>
       </c>
-      <c r="C953" t="s">
+      <c r="D953" t="s">
         <v>9307</v>
       </c>
-      <c r="D953" t="s">
+      <c r="E953" t="s">
         <v>9308</v>
-      </c>
-      <c r="E953" t="s">
-        <v>9309</v>
       </c>
       <c r="F953" t="s">
         <v>5496</v>
@@ -57209,24 +57206,24 @@
         <v>8521</v>
       </c>
       <c r="I953" t="s">
-        <v>9310</v>
+        <v>9309</v>
       </c>
     </row>
     <row r="954" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A954" t="s">
+        <v>9310</v>
+      </c>
+      <c r="B954" t="s">
         <v>9311</v>
       </c>
-      <c r="B954" t="s">
+      <c r="C954" t="s">
         <v>9312</v>
       </c>
-      <c r="C954" t="s">
+      <c r="D954" t="s">
         <v>9313</v>
       </c>
-      <c r="D954" t="s">
+      <c r="E954" t="s">
         <v>9314</v>
-      </c>
-      <c r="E954" t="s">
-        <v>9315</v>
       </c>
       <c r="F954" t="s">
         <v>5496</v>
@@ -57240,19 +57237,19 @@
     </row>
     <row r="955" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A955" t="s">
+        <v>9315</v>
+      </c>
+      <c r="B955" t="s">
         <v>9316</v>
       </c>
-      <c r="B955" t="s">
+      <c r="C955" t="s">
         <v>9317</v>
       </c>
-      <c r="C955" t="s">
+      <c r="D955" t="s">
         <v>9318</v>
       </c>
-      <c r="D955" t="s">
+      <c r="E955" t="s">
         <v>9319</v>
-      </c>
-      <c r="E955" t="s">
-        <v>9320</v>
       </c>
       <c r="F955" t="s">
         <v>5496</v>
@@ -57266,19 +57263,19 @@
     </row>
     <row r="956" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A956" t="s">
+        <v>9320</v>
+      </c>
+      <c r="B956" t="s">
         <v>9321</v>
       </c>
-      <c r="B956" t="s">
+      <c r="C956" t="s">
         <v>9322</v>
       </c>
-      <c r="C956" t="s">
+      <c r="D956" t="s">
         <v>9323</v>
       </c>
-      <c r="D956" t="s">
+      <c r="E956" t="s">
         <v>9324</v>
-      </c>
-      <c r="E956" t="s">
-        <v>9325</v>
       </c>
       <c r="F956" t="s">
         <v>5496</v>
@@ -57290,76 +57287,76 @@
         <v>5503</v>
       </c>
       <c r="I956" t="s">
-        <v>9326</v>
+        <v>9325</v>
       </c>
     </row>
     <row r="957" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A957" t="s">
+        <v>9326</v>
+      </c>
+      <c r="B957" t="s">
         <v>9327</v>
       </c>
-      <c r="B957" t="s">
+      <c r="C957" t="s">
         <v>9328</v>
       </c>
-      <c r="C957" t="s">
+      <c r="D957" t="s">
         <v>9329</v>
       </c>
-      <c r="D957" t="s">
+      <c r="E957" t="s">
         <v>9330</v>
       </c>
-      <c r="E957" t="s">
+      <c r="F957" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G957" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H957" t="s">
         <v>9331</v>
-      </c>
-      <c r="F957" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G957" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H957" t="s">
-        <v>9332</v>
       </c>
     </row>
     <row r="958" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A958" t="s">
+        <v>9332</v>
+      </c>
+      <c r="B958" t="s">
         <v>9333</v>
       </c>
-      <c r="B958" t="s">
+      <c r="C958" t="s">
         <v>9334</v>
       </c>
-      <c r="C958" t="s">
+      <c r="D958" t="s">
         <v>9335</v>
       </c>
-      <c r="D958" t="s">
+      <c r="E958" t="s">
         <v>9336</v>
       </c>
-      <c r="E958" t="s">
+      <c r="F958" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G958" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H958" t="s">
         <v>9337</v>
-      </c>
-      <c r="F958" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G958" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H958" t="s">
-        <v>9338</v>
       </c>
     </row>
     <row r="959" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A959" t="s">
+        <v>9338</v>
+      </c>
+      <c r="B959" t="s">
         <v>9339</v>
       </c>
-      <c r="B959" t="s">
+      <c r="C959" t="s">
         <v>9340</v>
       </c>
-      <c r="C959" t="s">
+      <c r="D959" t="s">
         <v>9341</v>
       </c>
-      <c r="D959" t="s">
+      <c r="E959" t="s">
         <v>9342</v>
-      </c>
-      <c r="E959" t="s">
-        <v>9343</v>
       </c>
       <c r="F959" t="s">
         <v>5496</v>
@@ -57373,19 +57370,19 @@
     </row>
     <row r="960" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A960" t="s">
+        <v>9343</v>
+      </c>
+      <c r="B960" t="s">
         <v>9344</v>
       </c>
-      <c r="B960" t="s">
+      <c r="C960" t="s">
         <v>9345</v>
       </c>
-      <c r="C960" t="s">
+      <c r="D960" t="s">
         <v>9346</v>
       </c>
-      <c r="D960" t="s">
+      <c r="E960" t="s">
         <v>9347</v>
-      </c>
-      <c r="E960" t="s">
-        <v>9348</v>
       </c>
       <c r="F960" t="s">
         <v>5496</v>
@@ -57399,71 +57396,71 @@
     </row>
     <row r="961" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A961" t="s">
+        <v>9348</v>
+      </c>
+      <c r="B961" t="s">
         <v>9349</v>
       </c>
-      <c r="B961" t="s">
+      <c r="C961" t="s">
         <v>9350</v>
       </c>
-      <c r="C961" t="s">
+      <c r="D961" t="s">
         <v>9351</v>
       </c>
-      <c r="D961" t="s">
+      <c r="E961" t="s">
         <v>9352</v>
       </c>
-      <c r="E961" t="s">
+      <c r="F961" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G961" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H961" t="s">
         <v>9353</v>
-      </c>
-      <c r="F961" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G961" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H961" t="s">
-        <v>9354</v>
       </c>
     </row>
     <row r="962" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A962" t="s">
+        <v>9354</v>
+      </c>
+      <c r="B962" t="s">
         <v>9355</v>
       </c>
-      <c r="B962" t="s">
+      <c r="C962" t="s">
         <v>9356</v>
       </c>
-      <c r="C962" t="s">
+      <c r="D962" t="s">
         <v>9357</v>
       </c>
-      <c r="D962" t="s">
+      <c r="E962" t="s">
         <v>9358</v>
       </c>
-      <c r="E962" t="s">
+      <c r="F962" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G962" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H962" t="s">
         <v>9359</v>
-      </c>
-      <c r="F962" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G962" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H962" t="s">
-        <v>9360</v>
       </c>
     </row>
     <row r="963" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A963" t="s">
+        <v>9360</v>
+      </c>
+      <c r="B963" t="s">
         <v>9361</v>
       </c>
-      <c r="B963" t="s">
+      <c r="C963" t="s">
         <v>9362</v>
       </c>
-      <c r="C963" t="s">
+      <c r="D963" t="s">
         <v>9363</v>
       </c>
-      <c r="D963" t="s">
+      <c r="E963" t="s">
         <v>9364</v>
-      </c>
-      <c r="E963" t="s">
-        <v>9365</v>
       </c>
       <c r="F963" t="s">
         <v>5496</v>
@@ -57477,71 +57474,71 @@
     </row>
     <row r="964" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A964" t="s">
+        <v>9365</v>
+      </c>
+      <c r="B964" t="s">
         <v>9366</v>
       </c>
-      <c r="B964" t="s">
+      <c r="C964" t="s">
         <v>9367</v>
       </c>
-      <c r="C964" t="s">
+      <c r="D964" t="s">
         <v>9368</v>
       </c>
-      <c r="D964" t="s">
+      <c r="E964" t="s">
         <v>9369</v>
       </c>
-      <c r="E964" t="s">
+      <c r="F964" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G964" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H964" t="s">
         <v>9370</v>
-      </c>
-      <c r="F964" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G964" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H964" t="s">
-        <v>9371</v>
       </c>
     </row>
     <row r="965" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A965" t="s">
+        <v>9371</v>
+      </c>
+      <c r="B965" t="s">
         <v>9372</v>
       </c>
-      <c r="B965" t="s">
+      <c r="C965" t="s">
         <v>9373</v>
       </c>
-      <c r="C965" t="s">
+      <c r="D965" t="s">
         <v>9374</v>
       </c>
-      <c r="D965" t="s">
+      <c r="E965" t="s">
         <v>9375</v>
       </c>
-      <c r="E965" t="s">
+      <c r="F965" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G965" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H965" t="s">
         <v>9376</v>
-      </c>
-      <c r="F965" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G965" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H965" t="s">
-        <v>9377</v>
       </c>
     </row>
     <row r="966" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A966" t="s">
+        <v>9377</v>
+      </c>
+      <c r="B966" t="s">
         <v>9378</v>
       </c>
-      <c r="B966" t="s">
+      <c r="C966" t="s">
         <v>9379</v>
       </c>
-      <c r="C966" t="s">
+      <c r="D966" t="s">
         <v>9380</v>
       </c>
-      <c r="D966" t="s">
+      <c r="E966" t="s">
         <v>9381</v>
-      </c>
-      <c r="E966" t="s">
-        <v>9382</v>
       </c>
       <c r="F966" t="s">
         <v>5496</v>
@@ -57555,71 +57552,71 @@
     </row>
     <row r="967" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A967" t="s">
+        <v>9382</v>
+      </c>
+      <c r="B967" t="s">
         <v>9383</v>
       </c>
-      <c r="B967" t="s">
+      <c r="C967" t="s">
         <v>9384</v>
       </c>
-      <c r="C967" t="s">
+      <c r="D967" t="s">
         <v>9385</v>
       </c>
-      <c r="D967" t="s">
+      <c r="E967" t="s">
         <v>9386</v>
       </c>
-      <c r="E967" t="s">
+      <c r="F967" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G967" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H967" t="s">
         <v>9387</v>
-      </c>
-      <c r="F967" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G967" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H967" t="s">
-        <v>9388</v>
       </c>
     </row>
     <row r="968" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A968" t="s">
+        <v>9388</v>
+      </c>
+      <c r="B968" t="s">
         <v>9389</v>
       </c>
-      <c r="B968" t="s">
+      <c r="C968" t="s">
         <v>9390</v>
       </c>
-      <c r="C968" t="s">
+      <c r="D968" t="s">
         <v>9391</v>
       </c>
-      <c r="D968" t="s">
+      <c r="E968" t="s">
         <v>9392</v>
       </c>
-      <c r="E968" t="s">
+      <c r="F968" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G968" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H968" t="s">
         <v>9393</v>
-      </c>
-      <c r="F968" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G968" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H968" t="s">
-        <v>9394</v>
       </c>
     </row>
     <row r="969" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A969" t="s">
-        <v>9395</v>
+        <v>9394</v>
       </c>
       <c r="B969" t="s">
         <v>7134</v>
       </c>
       <c r="C969" t="s">
+        <v>9395</v>
+      </c>
+      <c r="D969" t="s">
         <v>9396</v>
       </c>
-      <c r="D969" t="s">
+      <c r="E969" t="s">
         <v>9397</v>
-      </c>
-      <c r="E969" t="s">
-        <v>9398</v>
       </c>
       <c r="F969" t="s">
         <v>5496</v>
@@ -57633,45 +57630,45 @@
     </row>
     <row r="970" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A970" t="s">
+        <v>9398</v>
+      </c>
+      <c r="B970" t="s">
         <v>9399</v>
       </c>
-      <c r="B970" t="s">
+      <c r="C970" t="s">
         <v>9400</v>
       </c>
-      <c r="C970" t="s">
+      <c r="D970" t="s">
         <v>9401</v>
       </c>
-      <c r="D970" t="s">
+      <c r="E970" t="s">
         <v>9402</v>
       </c>
-      <c r="E970" t="s">
+      <c r="F970" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G970" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H970" t="s">
         <v>9403</v>
-      </c>
-      <c r="F970" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G970" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H970" t="s">
-        <v>9404</v>
       </c>
     </row>
     <row r="971" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A971" t="s">
+        <v>9404</v>
+      </c>
+      <c r="B971" t="s">
         <v>9405</v>
       </c>
-      <c r="B971" t="s">
+      <c r="C971" t="s">
         <v>9406</v>
       </c>
-      <c r="C971" t="s">
+      <c r="D971" t="s">
         <v>9407</v>
       </c>
-      <c r="D971" t="s">
+      <c r="E971" t="s">
         <v>9408</v>
-      </c>
-      <c r="E971" t="s">
-        <v>9409</v>
       </c>
       <c r="F971" t="s">
         <v>5496</v>
@@ -57685,74 +57682,74 @@
     </row>
     <row r="972" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A972" t="s">
+        <v>9409</v>
+      </c>
+      <c r="B972" t="s">
         <v>9410</v>
       </c>
-      <c r="B972" t="s">
+      <c r="C972" t="s">
         <v>9411</v>
       </c>
-      <c r="C972" t="s">
+      <c r="D972" t="s">
         <v>9412</v>
       </c>
-      <c r="D972" t="s">
+      <c r="E972" t="s">
         <v>9413</v>
       </c>
-      <c r="E972" t="s">
+      <c r="F972" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G972" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H972" t="s">
         <v>9414</v>
-      </c>
-      <c r="F972" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G972" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H972" t="s">
-        <v>9415</v>
       </c>
     </row>
     <row r="973" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A973" t="s">
+        <v>9415</v>
+      </c>
+      <c r="B973" t="s">
         <v>9416</v>
       </c>
-      <c r="B973" t="s">
+      <c r="C973" t="s">
         <v>9417</v>
       </c>
-      <c r="C973" t="s">
+      <c r="D973" t="s">
         <v>9418</v>
       </c>
-      <c r="D973" t="s">
+      <c r="E973" t="s">
         <v>9419</v>
       </c>
-      <c r="E973" t="s">
+      <c r="F973" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G973" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H973" t="s">
         <v>9420</v>
       </c>
-      <c r="F973" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G973" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H973" t="s">
+      <c r="I973" t="s">
         <v>9421</v>
-      </c>
-      <c r="I973" t="s">
-        <v>9422</v>
       </c>
     </row>
     <row r="974" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A974" t="s">
+        <v>9422</v>
+      </c>
+      <c r="B974" t="s">
         <v>9423</v>
       </c>
-      <c r="B974" t="s">
+      <c r="C974" t="s">
         <v>9424</v>
       </c>
-      <c r="C974" t="s">
+      <c r="D974" t="s">
         <v>9425</v>
       </c>
-      <c r="D974" t="s">
+      <c r="E974" t="s">
         <v>9426</v>
-      </c>
-      <c r="E974" t="s">
-        <v>9427</v>
       </c>
       <c r="F974" t="s">
         <v>5496</v>
@@ -57766,20 +57763,20 @@
     </row>
     <row r="975" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A975" t="s">
+        <v>9427</v>
+      </c>
+      <c r="B975" t="s">
         <v>9428</v>
       </c>
-      <c r="B975" t="s">
+      <c r="C975" t="s">
         <v>9429</v>
       </c>
-      <c r="C975" t="s">
+      <c r="D975" t="s">
         <v>9430</v>
       </c>
-      <c r="D975" t="s">
+      <c r="E975" t="s">
         <v>9431</v>
       </c>
-      <c r="E975" t="s">
-        <v>9432</v>
-      </c>
       <c r="F975" t="s">
         <v>5496</v>
       </c>
@@ -57787,25 +57784,25 @@
         <v>5496</v>
       </c>
       <c r="H975" t="s">
-        <v>9304</v>
+        <v>9303</v>
       </c>
     </row>
     <row r="976" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A976" t="s">
-        <v>9433</v>
+        <v>9432</v>
       </c>
       <c r="B976" t="s">
         <v>3652</v>
       </c>
       <c r="C976" t="s">
+        <v>9433</v>
+      </c>
+      <c r="D976" t="s">
         <v>9434</v>
       </c>
-      <c r="D976" t="s">
+      <c r="E976" t="s">
         <v>9435</v>
       </c>
-      <c r="E976" t="s">
-        <v>9436</v>
-      </c>
       <c r="F976" t="s">
         <v>5496</v>
       </c>
@@ -57813,102 +57810,102 @@
         <v>5496</v>
       </c>
       <c r="H976" t="s">
-        <v>9255</v>
+        <v>9254</v>
       </c>
     </row>
     <row r="977" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A977" t="s">
+        <v>9436</v>
+      </c>
+      <c r="B977" t="s">
         <v>9437</v>
       </c>
-      <c r="B977" t="s">
+      <c r="C977" t="s">
         <v>9438</v>
       </c>
-      <c r="C977" t="s">
+      <c r="D977" t="s">
         <v>9439</v>
       </c>
-      <c r="D977" t="s">
+      <c r="E977" t="s">
         <v>9440</v>
       </c>
-      <c r="E977" t="s">
+      <c r="F977" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G977" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H977" t="s">
         <v>9441</v>
-      </c>
-      <c r="F977" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G977" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H977" t="s">
-        <v>9442</v>
       </c>
     </row>
     <row r="978" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A978" t="s">
+        <v>9442</v>
+      </c>
+      <c r="B978" t="s">
         <v>9443</v>
       </c>
-      <c r="B978" t="s">
+      <c r="C978" t="s">
         <v>9444</v>
       </c>
-      <c r="C978" t="s">
+      <c r="D978" t="s">
         <v>9445</v>
       </c>
-      <c r="D978" t="s">
+      <c r="E978" t="s">
         <v>9446</v>
       </c>
-      <c r="E978" t="s">
+      <c r="F978" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G978" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H978" t="s">
         <v>9447</v>
-      </c>
-      <c r="F978" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G978" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H978" t="s">
-        <v>9448</v>
       </c>
     </row>
     <row r="979" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A979" t="s">
+        <v>9448</v>
+      </c>
+      <c r="B979" t="s">
         <v>9449</v>
       </c>
-      <c r="B979" t="s">
+      <c r="C979" t="s">
         <v>9450</v>
       </c>
-      <c r="C979" t="s">
+      <c r="D979" t="s">
         <v>9451</v>
       </c>
-      <c r="D979" t="s">
+      <c r="E979" t="s">
         <v>9452</v>
       </c>
-      <c r="E979" t="s">
+      <c r="F979" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G979" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H979" t="s">
         <v>9453</v>
-      </c>
-      <c r="F979" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G979" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H979" t="s">
-        <v>9454</v>
       </c>
     </row>
     <row r="980" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A980" t="s">
+        <v>9454</v>
+      </c>
+      <c r="B980" t="s">
         <v>9455</v>
       </c>
-      <c r="B980" t="s">
+      <c r="C980" t="s">
         <v>9456</v>
       </c>
-      <c r="C980" t="s">
+      <c r="D980" t="s">
         <v>9457</v>
       </c>
-      <c r="D980" t="s">
+      <c r="E980" t="s">
         <v>9458</v>
-      </c>
-      <c r="E980" t="s">
-        <v>9459</v>
       </c>
       <c r="F980" t="s">
         <v>5496</v>
@@ -57920,24 +57917,24 @@
         <v>6514</v>
       </c>
       <c r="I980" t="s">
-        <v>9460</v>
+        <v>9459</v>
       </c>
     </row>
     <row r="981" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A981" t="s">
+        <v>9460</v>
+      </c>
+      <c r="B981" t="s">
         <v>9461</v>
       </c>
-      <c r="B981" t="s">
+      <c r="C981" t="s">
         <v>9462</v>
       </c>
-      <c r="C981" t="s">
+      <c r="D981" t="s">
         <v>9463</v>
       </c>
-      <c r="D981" t="s">
+      <c r="E981" t="s">
         <v>9464</v>
-      </c>
-      <c r="E981" t="s">
-        <v>9465</v>
       </c>
       <c r="F981" t="s">
         <v>5496</v>
@@ -57949,102 +57946,102 @@
         <v>6230</v>
       </c>
       <c r="I981" t="s">
-        <v>9466</v>
+        <v>9465</v>
       </c>
     </row>
     <row r="982" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A982" t="s">
+        <v>9466</v>
+      </c>
+      <c r="B982" t="s">
         <v>9467</v>
       </c>
-      <c r="B982" t="s">
+      <c r="C982" t="s">
         <v>9468</v>
       </c>
-      <c r="C982" t="s">
+      <c r="D982" t="s">
         <v>9469</v>
       </c>
-      <c r="D982" t="s">
+      <c r="E982" t="s">
         <v>9470</v>
       </c>
-      <c r="E982" t="s">
+      <c r="F982" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G982" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H982" t="s">
         <v>9471</v>
-      </c>
-      <c r="F982" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G982" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H982" t="s">
-        <v>9472</v>
       </c>
     </row>
     <row r="983" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A983" t="s">
+        <v>9472</v>
+      </c>
+      <c r="B983" t="s">
         <v>9473</v>
       </c>
-      <c r="B983" t="s">
+      <c r="C983" t="s">
         <v>9474</v>
       </c>
-      <c r="C983" t="s">
+      <c r="D983" t="s">
         <v>9475</v>
       </c>
-      <c r="D983" t="s">
+      <c r="E983" t="s">
         <v>9476</v>
       </c>
-      <c r="E983" t="s">
+      <c r="F983" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G983" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H983" t="s">
         <v>9477</v>
-      </c>
-      <c r="F983" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G983" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H983" t="s">
-        <v>9478</v>
       </c>
     </row>
     <row r="984" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A984" t="s">
+        <v>9478</v>
+      </c>
+      <c r="B984" t="s">
         <v>9479</v>
       </c>
-      <c r="B984" t="s">
+      <c r="C984" t="s">
         <v>9480</v>
       </c>
-      <c r="C984" t="s">
+      <c r="D984" t="s">
         <v>9481</v>
       </c>
-      <c r="D984" t="s">
+      <c r="E984" t="s">
         <v>9482</v>
       </c>
-      <c r="E984" t="s">
+      <c r="F984" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G984" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H984" t="s">
         <v>9483</v>
-      </c>
-      <c r="F984" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G984" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H984" t="s">
-        <v>9484</v>
       </c>
     </row>
     <row r="985" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A985" t="s">
+        <v>9484</v>
+      </c>
+      <c r="B985" t="s">
         <v>9485</v>
       </c>
-      <c r="B985" t="s">
+      <c r="C985" t="s">
         <v>9486</v>
       </c>
-      <c r="C985" t="s">
+      <c r="D985" t="s">
         <v>9487</v>
       </c>
-      <c r="D985" t="s">
+      <c r="E985" t="s">
         <v>9488</v>
-      </c>
-      <c r="E985" t="s">
-        <v>9489</v>
       </c>
       <c r="F985" t="s">
         <v>5496</v>
@@ -58058,77 +58055,77 @@
     </row>
     <row r="986" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A986" t="s">
+        <v>9489</v>
+      </c>
+      <c r="B986" t="s">
         <v>9490</v>
       </c>
-      <c r="B986" t="s">
+      <c r="C986" t="s">
         <v>9491</v>
       </c>
-      <c r="C986" t="s">
+      <c r="D986" t="s">
         <v>9492</v>
       </c>
-      <c r="D986" t="s">
+      <c r="E986" t="s">
         <v>9493</v>
       </c>
-      <c r="E986" t="s">
+      <c r="F986" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G986" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H986" t="s">
         <v>9494</v>
       </c>
-      <c r="F986" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G986" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H986" t="s">
+      <c r="I986" t="s">
         <v>9495</v>
-      </c>
-      <c r="I986" t="s">
-        <v>9496</v>
       </c>
     </row>
     <row r="987" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A987" t="s">
+        <v>9496</v>
+      </c>
+      <c r="B987" t="s">
         <v>9497</v>
       </c>
-      <c r="B987" t="s">
+      <c r="C987" t="s">
         <v>9498</v>
       </c>
-      <c r="C987" t="s">
+      <c r="D987" t="s">
         <v>9499</v>
       </c>
-      <c r="D987" t="s">
+      <c r="E987" t="s">
         <v>9500</v>
       </c>
-      <c r="E987" t="s">
+      <c r="F987" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G987" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H987" t="s">
         <v>9501</v>
       </c>
-      <c r="F987" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G987" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H987" t="s">
+      <c r="I987" t="s">
         <v>9502</v>
-      </c>
-      <c r="I987" t="s">
-        <v>9503</v>
       </c>
     </row>
     <row r="988" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A988" t="s">
+        <v>9503</v>
+      </c>
+      <c r="B988" t="s">
         <v>9504</v>
       </c>
-      <c r="B988" t="s">
+      <c r="C988" t="s">
         <v>9505</v>
       </c>
-      <c r="C988" t="s">
+      <c r="D988" t="s">
         <v>9506</v>
       </c>
-      <c r="D988" t="s">
+      <c r="E988" t="s">
         <v>9507</v>
-      </c>
-      <c r="E988" t="s">
-        <v>9508</v>
       </c>
       <c r="F988" t="s">
         <v>5496</v>
@@ -58140,7 +58137,7 @@
         <v>4688</v>
       </c>
       <c r="I988" t="s">
-        <v>9509</v>
+        <v>9508</v>
       </c>
     </row>
     <row r="989" spans="1:9" x14ac:dyDescent="0.3">
@@ -58154,7 +58151,7 @@
         <v>3977</v>
       </c>
       <c r="D989" t="s">
-        <v>9510</v>
+        <v>9509</v>
       </c>
       <c r="E989" t="s">
         <v>4938</v>
@@ -58174,19 +58171,19 @@
     </row>
     <row r="990" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A990" t="s">
+        <v>9510</v>
+      </c>
+      <c r="B990" t="s">
         <v>9511</v>
       </c>
-      <c r="B990" t="s">
+      <c r="C990" t="s">
         <v>9512</v>
       </c>
-      <c r="C990" t="s">
+      <c r="D990" t="s">
         <v>9513</v>
       </c>
-      <c r="D990" t="s">
+      <c r="E990" t="s">
         <v>9514</v>
-      </c>
-      <c r="E990" t="s">
-        <v>9515</v>
       </c>
       <c r="F990" t="s">
         <v>5496</v>
@@ -58198,24 +58195,24 @@
         <v>4688</v>
       </c>
       <c r="I990" t="s">
-        <v>9516</v>
+        <v>9515</v>
       </c>
     </row>
     <row r="991" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A991" t="s">
-        <v>9517</v>
+        <v>9516</v>
       </c>
       <c r="B991" t="s">
         <v>6834</v>
       </c>
       <c r="C991" t="s">
+        <v>9517</v>
+      </c>
+      <c r="D991" t="s">
         <v>9518</v>
       </c>
-      <c r="D991" t="s">
+      <c r="E991" t="s">
         <v>9519</v>
-      </c>
-      <c r="E991" t="s">
-        <v>9520</v>
       </c>
       <c r="F991" t="s">
         <v>5496</v>
@@ -58227,7 +58224,7 @@
         <v>4688</v>
       </c>
       <c r="I991" t="s">
-        <v>9521</v>
+        <v>9520</v>
       </c>
     </row>
     <row r="992" spans="1:9" x14ac:dyDescent="0.3">
@@ -58241,7 +58238,7 @@
         <v>3896</v>
       </c>
       <c r="D992" t="s">
-        <v>9522</v>
+        <v>9521</v>
       </c>
       <c r="E992" t="s">
         <v>4687</v>
@@ -58261,57 +58258,57 @@
     </row>
     <row r="993" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A993" t="s">
+        <v>9522</v>
+      </c>
+      <c r="B993" t="s">
         <v>9523</v>
       </c>
-      <c r="B993" t="s">
+      <c r="C993" t="s">
         <v>9524</v>
       </c>
-      <c r="C993" t="s">
+      <c r="D993" t="s">
         <v>9525</v>
       </c>
-      <c r="D993" t="s">
+      <c r="E993" t="s">
         <v>9526</v>
       </c>
-      <c r="E993" t="s">
+      <c r="F993" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G993" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H993" t="s">
         <v>9527</v>
-      </c>
-      <c r="F993" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G993" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H993" t="s">
-        <v>9528</v>
       </c>
     </row>
     <row r="994" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A994" t="s">
+        <v>9528</v>
+      </c>
+      <c r="B994" t="s">
         <v>9529</v>
       </c>
-      <c r="B994" t="s">
+      <c r="C994" t="s">
         <v>9530</v>
       </c>
-      <c r="C994" t="s">
+      <c r="D994" t="s">
         <v>9531</v>
       </c>
-      <c r="D994" t="s">
+      <c r="E994" t="s">
         <v>9532</v>
       </c>
-      <c r="E994" t="s">
+      <c r="F994" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G994" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H994" t="s">
         <v>9533</v>
       </c>
-      <c r="F994" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G994" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H994" t="s">
+      <c r="I994" t="s">
         <v>9534</v>
-      </c>
-      <c r="I994" t="s">
-        <v>9535</v>
       </c>
     </row>
     <row r="995" spans="1:9" x14ac:dyDescent="0.3">
@@ -58325,7 +58322,7 @@
         <v>3906</v>
       </c>
       <c r="D995" t="s">
-        <v>9536</v>
+        <v>9535</v>
       </c>
       <c r="E995" t="s">
         <v>4721</v>
@@ -58345,19 +58342,19 @@
     </row>
     <row r="996" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A996" t="s">
+        <v>9536</v>
+      </c>
+      <c r="B996" t="s">
         <v>9537</v>
       </c>
-      <c r="B996" t="s">
+      <c r="C996" t="s">
         <v>9538</v>
       </c>
-      <c r="C996" t="s">
+      <c r="D996" t="s">
         <v>9539</v>
       </c>
-      <c r="D996" t="s">
+      <c r="E996" t="s">
         <v>9540</v>
-      </c>
-      <c r="E996" t="s">
-        <v>9541</v>
       </c>
       <c r="F996" t="s">
         <v>5496</v>
@@ -58371,19 +58368,19 @@
     </row>
     <row r="997" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A997" t="s">
+        <v>9541</v>
+      </c>
+      <c r="B997" t="s">
         <v>9542</v>
       </c>
-      <c r="B997" t="s">
+      <c r="C997" t="s">
         <v>9543</v>
       </c>
-      <c r="C997" t="s">
+      <c r="D997" t="s">
         <v>9544</v>
       </c>
-      <c r="D997" t="s">
+      <c r="E997" t="s">
         <v>9545</v>
-      </c>
-      <c r="E997" t="s">
-        <v>9546</v>
       </c>
       <c r="F997" t="s">
         <v>5496</v>
@@ -58397,60 +58394,60 @@
     </row>
     <row r="998" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A998" t="s">
-        <v>9547</v>
+        <v>9546</v>
       </c>
       <c r="B998" t="s">
         <v>3601</v>
       </c>
       <c r="C998" t="s">
+        <v>9547</v>
+      </c>
+      <c r="D998" t="s">
         <v>9548</v>
       </c>
-      <c r="D998" t="s">
+      <c r="E998" t="s">
         <v>9549</v>
       </c>
-      <c r="E998" t="s">
+      <c r="F998" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G998" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H998" t="s">
         <v>9550</v>
       </c>
-      <c r="F998" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G998" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H998" t="s">
+      <c r="I998" t="s">
         <v>9551</v>
-      </c>
-      <c r="I998" t="s">
-        <v>9552</v>
       </c>
     </row>
     <row r="999" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A999" t="s">
+        <v>9552</v>
+      </c>
+      <c r="B999" t="s">
         <v>9553</v>
       </c>
-      <c r="B999" t="s">
+      <c r="C999" t="s">
         <v>9554</v>
       </c>
-      <c r="C999" t="s">
+      <c r="D999" t="s">
         <v>9555</v>
       </c>
-      <c r="D999" t="s">
+      <c r="E999" t="s">
         <v>9556</v>
       </c>
-      <c r="E999" t="s">
+      <c r="F999" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G999" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H999" t="s">
         <v>9557</v>
       </c>
-      <c r="F999" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G999" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H999" t="s">
+      <c r="I999" t="s">
         <v>9558</v>
-      </c>
-      <c r="I999" t="s">
-        <v>9559</v>
       </c>
     </row>
     <row r="1000" spans="1:9" x14ac:dyDescent="0.3">
@@ -58464,7 +58461,7 @@
         <v>3941</v>
       </c>
       <c r="D1000" t="s">
-        <v>9560</v>
+        <v>9559</v>
       </c>
       <c r="E1000" t="s">
         <v>4825</v>
@@ -58484,48 +58481,48 @@
     </row>
     <row r="1001" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1001" t="s">
+        <v>9560</v>
+      </c>
+      <c r="B1001" t="s">
         <v>9561</v>
       </c>
-      <c r="B1001" t="s">
+      <c r="C1001" t="s">
         <v>9562</v>
       </c>
-      <c r="C1001" t="s">
+      <c r="D1001" t="s">
         <v>9563</v>
       </c>
-      <c r="D1001" t="s">
+      <c r="E1001" t="s">
         <v>9564</v>
       </c>
-      <c r="E1001" t="s">
+      <c r="F1001" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1001" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1001" t="s">
         <v>9565</v>
       </c>
-      <c r="F1001" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1001" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1001" t="s">
+      <c r="I1001" t="s">
         <v>9566</v>
-      </c>
-      <c r="I1001" t="s">
-        <v>9567</v>
       </c>
     </row>
     <row r="1002" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1002" t="s">
+        <v>9567</v>
+      </c>
+      <c r="B1002" t="s">
         <v>9568</v>
       </c>
-      <c r="B1002" t="s">
+      <c r="C1002" t="s">
         <v>9569</v>
       </c>
-      <c r="C1002" t="s">
+      <c r="D1002" t="s">
         <v>9570</v>
       </c>
-      <c r="D1002" t="s">
+      <c r="E1002" t="s">
         <v>9571</v>
-      </c>
-      <c r="E1002" t="s">
-        <v>9572</v>
       </c>
       <c r="F1002" t="s">
         <v>5496</v>
@@ -58539,31 +58536,31 @@
     </row>
     <row r="1003" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1003" t="s">
+        <v>9572</v>
+      </c>
+      <c r="B1003" t="s">
         <v>9573</v>
       </c>
-      <c r="B1003" t="s">
+      <c r="C1003" t="s">
         <v>9574</v>
       </c>
-      <c r="C1003" t="s">
+      <c r="D1003" t="s">
         <v>9575</v>
       </c>
-      <c r="D1003" t="s">
+      <c r="E1003" t="s">
         <v>9576</v>
       </c>
-      <c r="E1003" t="s">
+      <c r="F1003" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1003" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1003" t="s">
         <v>9577</v>
       </c>
-      <c r="F1003" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1003" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1003" t="s">
+      <c r="I1003" t="s">
         <v>9578</v>
-      </c>
-      <c r="I1003" t="s">
-        <v>9579</v>
       </c>
     </row>
     <row r="1004" spans="1:9" x14ac:dyDescent="0.3">
@@ -58577,7 +58574,7 @@
         <v>3944</v>
       </c>
       <c r="D1004" t="s">
-        <v>9580</v>
+        <v>9579</v>
       </c>
       <c r="E1004" t="s">
         <v>4833</v>
@@ -58589,7 +58586,7 @@
         <v>5496</v>
       </c>
       <c r="H1004" t="s">
-        <v>9581</v>
+        <v>9580</v>
       </c>
       <c r="I1004" t="s">
         <v>4835</v>
@@ -58597,19 +58594,19 @@
     </row>
     <row r="1005" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1005" t="s">
+        <v>9581</v>
+      </c>
+      <c r="B1005" t="s">
         <v>9582</v>
       </c>
-      <c r="B1005" t="s">
+      <c r="C1005" t="s">
         <v>9583</v>
       </c>
-      <c r="C1005" t="s">
+      <c r="D1005" t="s">
         <v>9584</v>
       </c>
-      <c r="D1005" t="s">
+      <c r="E1005" t="s">
         <v>9585</v>
-      </c>
-      <c r="E1005" t="s">
-        <v>9586</v>
       </c>
       <c r="F1005" t="s">
         <v>5496</v>
@@ -58621,230 +58618,230 @@
         <v>4688</v>
       </c>
       <c r="I1005" t="s">
-        <v>9587</v>
+        <v>9586</v>
       </c>
     </row>
     <row r="1006" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1006" t="s">
+        <v>9587</v>
+      </c>
+      <c r="B1006" t="s">
         <v>9588</v>
       </c>
-      <c r="B1006" t="s">
+      <c r="C1006" t="s">
         <v>9589</v>
       </c>
-      <c r="C1006" t="s">
+      <c r="D1006" t="s">
         <v>9590</v>
       </c>
-      <c r="D1006" t="s">
+      <c r="E1006" t="s">
         <v>9591</v>
       </c>
-      <c r="E1006" t="s">
+      <c r="F1006" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1006" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1006" t="s">
         <v>9592</v>
-      </c>
-      <c r="F1006" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1006" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1006" t="s">
-        <v>9593</v>
       </c>
     </row>
     <row r="1007" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1007" t="s">
+        <v>9593</v>
+      </c>
+      <c r="B1007" t="s">
         <v>9594</v>
       </c>
-      <c r="B1007" t="s">
+      <c r="C1007" t="s">
         <v>9595</v>
       </c>
-      <c r="C1007" t="s">
+      <c r="D1007" t="s">
         <v>9596</v>
       </c>
-      <c r="D1007" t="s">
+      <c r="E1007" t="s">
         <v>9597</v>
       </c>
-      <c r="E1007" t="s">
+      <c r="F1007" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1007" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1007" t="s">
         <v>9598</v>
       </c>
-      <c r="F1007" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1007" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1007" t="s">
+      <c r="I1007" t="s">
         <v>9599</v>
-      </c>
-      <c r="I1007" t="s">
-        <v>9600</v>
       </c>
     </row>
     <row r="1008" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1008" t="s">
+        <v>9600</v>
+      </c>
+      <c r="B1008" t="s">
         <v>9601</v>
       </c>
-      <c r="B1008" t="s">
+      <c r="C1008" t="s">
         <v>9602</v>
       </c>
-      <c r="C1008" t="s">
+      <c r="D1008" t="s">
         <v>9603</v>
       </c>
-      <c r="D1008" t="s">
+      <c r="E1008" t="s">
         <v>9604</v>
       </c>
-      <c r="E1008" t="s">
+      <c r="F1008" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1008" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1008" t="s">
         <v>9605</v>
       </c>
-      <c r="F1008" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1008" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1008" t="s">
+      <c r="I1008" t="s">
         <v>9606</v>
-      </c>
-      <c r="I1008" t="s">
-        <v>9607</v>
       </c>
     </row>
     <row r="1009" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1009" t="s">
+        <v>9607</v>
+      </c>
+      <c r="B1009" t="s">
         <v>9608</v>
       </c>
-      <c r="B1009" t="s">
+      <c r="C1009" t="s">
         <v>9609</v>
       </c>
-      <c r="C1009" t="s">
+      <c r="D1009" t="s">
         <v>9610</v>
       </c>
-      <c r="D1009" t="s">
+      <c r="E1009" t="s">
         <v>9611</v>
       </c>
-      <c r="E1009" t="s">
+      <c r="F1009" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1009" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1009" t="s">
         <v>9612</v>
-      </c>
-      <c r="F1009" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1009" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1009" t="s">
-        <v>9613</v>
       </c>
     </row>
     <row r="1010" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1010" t="s">
+        <v>9613</v>
+      </c>
+      <c r="B1010" t="s">
         <v>9614</v>
       </c>
-      <c r="B1010" t="s">
+      <c r="C1010" t="s">
         <v>9615</v>
       </c>
-      <c r="C1010" t="s">
+      <c r="D1010" t="s">
         <v>9616</v>
       </c>
-      <c r="D1010" t="s">
+      <c r="E1010" t="s">
         <v>9617</v>
       </c>
-      <c r="E1010" t="s">
+      <c r="F1010" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1010" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1010" t="s">
         <v>9618</v>
       </c>
-      <c r="F1010" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1010" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1010" t="s">
+      <c r="I1010" t="s">
         <v>9619</v>
-      </c>
-      <c r="I1010" t="s">
-        <v>9620</v>
       </c>
     </row>
     <row r="1011" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1011" t="s">
+        <v>9620</v>
+      </c>
+      <c r="B1011" t="s">
         <v>9621</v>
       </c>
-      <c r="B1011" t="s">
+      <c r="C1011" t="s">
         <v>9622</v>
       </c>
-      <c r="C1011" t="s">
+      <c r="D1011" t="s">
         <v>9623</v>
       </c>
-      <c r="D1011" t="s">
+      <c r="E1011" t="s">
         <v>9624</v>
       </c>
-      <c r="E1011" t="s">
+      <c r="F1011" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1011" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1011" t="s">
         <v>9625</v>
-      </c>
-      <c r="F1011" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1011" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1011" t="s">
-        <v>9626</v>
       </c>
     </row>
     <row r="1012" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1012" t="s">
+        <v>9626</v>
+      </c>
+      <c r="B1012" t="s">
         <v>9627</v>
       </c>
-      <c r="B1012" t="s">
+      <c r="C1012" t="s">
         <v>9628</v>
       </c>
-      <c r="C1012" t="s">
+      <c r="D1012" t="s">
         <v>9629</v>
       </c>
-      <c r="D1012" t="s">
+      <c r="E1012" t="s">
         <v>9630</v>
       </c>
-      <c r="E1012" t="s">
+      <c r="F1012" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1012" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1012" t="s">
         <v>9631</v>
       </c>
-      <c r="F1012" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1012" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1012" t="s">
+      <c r="I1012" t="s">
         <v>9632</v>
-      </c>
-      <c r="I1012" t="s">
-        <v>9633</v>
       </c>
     </row>
     <row r="1013" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1013" t="s">
+        <v>9633</v>
+      </c>
+      <c r="B1013" t="s">
         <v>9634</v>
       </c>
-      <c r="B1013" t="s">
+      <c r="C1013" t="s">
         <v>9635</v>
       </c>
-      <c r="C1013" t="s">
+      <c r="D1013" t="s">
         <v>9636</v>
       </c>
-      <c r="D1013" t="s">
+      <c r="E1013" t="s">
         <v>9637</v>
       </c>
-      <c r="E1013" t="s">
+      <c r="F1013" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1013" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1013" t="s">
         <v>9638</v>
       </c>
-      <c r="F1013" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1013" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1013" t="s">
+      <c r="I1013" t="s">
         <v>9639</v>
-      </c>
-      <c r="I1013" t="s">
-        <v>9640</v>
       </c>
     </row>
     <row r="1014" spans="1:9" x14ac:dyDescent="0.3">
@@ -58858,7 +58855,7 @@
         <v>3897</v>
       </c>
       <c r="D1014" t="s">
-        <v>9641</v>
+        <v>9640</v>
       </c>
       <c r="E1014" t="s">
         <v>4690</v>
@@ -58878,74 +58875,74 @@
     </row>
     <row r="1015" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1015" t="s">
+        <v>9641</v>
+      </c>
+      <c r="B1015" t="s">
         <v>9642</v>
       </c>
-      <c r="B1015" t="s">
+      <c r="C1015" t="s">
         <v>9643</v>
       </c>
-      <c r="C1015" t="s">
+      <c r="D1015" t="s">
         <v>9644</v>
       </c>
-      <c r="D1015" t="s">
+      <c r="E1015" t="s">
         <v>9645</v>
       </c>
-      <c r="E1015" t="s">
+      <c r="F1015" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1015" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1015" t="s">
         <v>9646</v>
       </c>
-      <c r="F1015" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1015" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1015" t="s">
+      <c r="I1015" t="s">
         <v>9647</v>
-      </c>
-      <c r="I1015" t="s">
-        <v>9648</v>
       </c>
     </row>
     <row r="1016" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1016" t="s">
+        <v>9648</v>
+      </c>
+      <c r="B1016" t="s">
         <v>9649</v>
       </c>
-      <c r="B1016" t="s">
+      <c r="C1016" t="s">
         <v>9650</v>
       </c>
-      <c r="C1016" t="s">
+      <c r="D1016" t="s">
         <v>9651</v>
       </c>
-      <c r="D1016" t="s">
+      <c r="E1016" t="s">
         <v>9652</v>
       </c>
-      <c r="E1016" t="s">
+      <c r="F1016" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1016" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1016" t="s">
         <v>9653</v>
-      </c>
-      <c r="F1016" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1016" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1016" t="s">
-        <v>9654</v>
       </c>
     </row>
     <row r="1017" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1017" t="s">
+        <v>9654</v>
+      </c>
+      <c r="B1017" t="s">
         <v>9655</v>
       </c>
-      <c r="B1017" t="s">
+      <c r="C1017" t="s">
         <v>9656</v>
       </c>
-      <c r="C1017" t="s">
+      <c r="D1017" t="s">
         <v>9657</v>
       </c>
-      <c r="D1017" t="s">
+      <c r="E1017" t="s">
         <v>9658</v>
-      </c>
-      <c r="E1017" t="s">
-        <v>9659</v>
       </c>
       <c r="F1017" t="s">
         <v>5496</v>
@@ -58959,1170 +58956,1170 @@
     </row>
     <row r="1018" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1018" t="s">
+        <v>9659</v>
+      </c>
+      <c r="B1018" t="s">
         <v>9660</v>
       </c>
-      <c r="B1018" t="s">
+      <c r="C1018" t="s">
         <v>9661</v>
       </c>
-      <c r="C1018" t="s">
+      <c r="D1018" t="s">
         <v>9662</v>
       </c>
-      <c r="D1018" t="s">
+      <c r="E1018" t="s">
         <v>9663</v>
       </c>
-      <c r="E1018" t="s">
+      <c r="F1018" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1018" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1018" t="s">
         <v>9664</v>
-      </c>
-      <c r="F1018" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1018" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1018" t="s">
-        <v>9665</v>
       </c>
     </row>
     <row r="1019" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1019" t="s">
+        <v>9665</v>
+      </c>
+      <c r="B1019" t="s">
         <v>9666</v>
       </c>
-      <c r="B1019" t="s">
+      <c r="C1019" t="s">
         <v>9667</v>
       </c>
-      <c r="C1019" t="s">
+      <c r="D1019" t="s">
         <v>9668</v>
       </c>
-      <c r="D1019" t="s">
+      <c r="E1019" t="s">
         <v>9669</v>
       </c>
-      <c r="E1019" t="s">
+      <c r="F1019" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1019" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1019" t="s">
         <v>9670</v>
       </c>
-      <c r="F1019" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1019" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1019" t="s">
+      <c r="I1019" t="s">
         <v>9671</v>
-      </c>
-      <c r="I1019" t="s">
-        <v>9672</v>
       </c>
     </row>
     <row r="1020" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1020" t="s">
+        <v>9672</v>
+      </c>
+      <c r="B1020" t="s">
         <v>9673</v>
       </c>
-      <c r="B1020" t="s">
+      <c r="C1020" t="s">
         <v>9674</v>
       </c>
-      <c r="C1020" t="s">
+      <c r="D1020" t="s">
         <v>9675</v>
       </c>
-      <c r="D1020" t="s">
+      <c r="E1020" t="s">
         <v>9676</v>
       </c>
-      <c r="E1020" t="s">
+      <c r="F1020" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1020" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1020" t="s">
         <v>9677</v>
       </c>
-      <c r="F1020" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1020" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1020" t="s">
+      <c r="I1020" t="s">
         <v>9678</v>
-      </c>
-      <c r="I1020" t="s">
-        <v>9679</v>
       </c>
     </row>
     <row r="1021" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1021" t="s">
+        <v>9679</v>
+      </c>
+      <c r="B1021" t="s">
         <v>9680</v>
       </c>
-      <c r="B1021" t="s">
+      <c r="C1021" t="s">
         <v>9681</v>
       </c>
-      <c r="C1021" t="s">
+      <c r="D1021" t="s">
         <v>9682</v>
       </c>
-      <c r="D1021" t="s">
+      <c r="E1021" t="s">
         <v>9683</v>
       </c>
-      <c r="E1021" t="s">
+      <c r="F1021" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1021" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1021" t="s">
         <v>9684</v>
       </c>
-      <c r="F1021" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1021" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1021" t="s">
+      <c r="I1021" t="s">
         <v>9685</v>
-      </c>
-      <c r="I1021" t="s">
-        <v>9686</v>
       </c>
     </row>
     <row r="1022" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1022" t="s">
+        <v>9686</v>
+      </c>
+      <c r="B1022" t="s">
         <v>9687</v>
       </c>
-      <c r="B1022" t="s">
+      <c r="C1022" t="s">
         <v>9688</v>
       </c>
-      <c r="C1022" t="s">
+      <c r="D1022" t="s">
         <v>9689</v>
       </c>
-      <c r="D1022" t="s">
+      <c r="E1022" t="s">
         <v>9690</v>
       </c>
-      <c r="E1022" t="s">
+      <c r="F1022" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1022" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1022" t="s">
         <v>9691</v>
       </c>
-      <c r="F1022" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1022" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1022" t="s">
+      <c r="I1022" t="s">
         <v>9692</v>
-      </c>
-      <c r="I1022" t="s">
-        <v>9693</v>
       </c>
     </row>
     <row r="1023" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1023" t="s">
+        <v>9693</v>
+      </c>
+      <c r="B1023" t="s">
         <v>9694</v>
       </c>
-      <c r="B1023" t="s">
+      <c r="C1023" t="s">
         <v>9695</v>
       </c>
-      <c r="C1023" t="s">
+      <c r="D1023" t="s">
         <v>9696</v>
       </c>
-      <c r="D1023" t="s">
+      <c r="E1023" t="s">
         <v>9697</v>
       </c>
-      <c r="E1023" t="s">
+      <c r="F1023" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1023" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1023" t="s">
         <v>9698</v>
       </c>
-      <c r="F1023" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1023" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1023" t="s">
+      <c r="I1023" t="s">
         <v>9699</v>
-      </c>
-      <c r="I1023" t="s">
-        <v>9700</v>
       </c>
     </row>
     <row r="1024" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1024" t="s">
+        <v>9700</v>
+      </c>
+      <c r="B1024" t="s">
         <v>9701</v>
       </c>
-      <c r="B1024" t="s">
+      <c r="C1024" t="s">
         <v>9702</v>
       </c>
-      <c r="C1024" t="s">
+      <c r="D1024" t="s">
         <v>9703</v>
       </c>
-      <c r="D1024" t="s">
+      <c r="E1024" t="s">
         <v>9704</v>
       </c>
-      <c r="E1024" t="s">
+      <c r="F1024" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1024" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1024" t="s">
         <v>9705</v>
       </c>
-      <c r="F1024" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1024" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1024" t="s">
+      <c r="I1024" t="s">
         <v>9706</v>
-      </c>
-      <c r="I1024" t="s">
-        <v>9707</v>
       </c>
     </row>
     <row r="1025" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1025" t="s">
+        <v>9707</v>
+      </c>
+      <c r="B1025" t="s">
         <v>9708</v>
       </c>
-      <c r="B1025" t="s">
+      <c r="C1025" t="s">
         <v>9709</v>
       </c>
-      <c r="C1025" t="s">
+      <c r="D1025" t="s">
         <v>9710</v>
       </c>
-      <c r="D1025" t="s">
+      <c r="E1025" t="s">
         <v>9711</v>
       </c>
-      <c r="E1025" t="s">
+      <c r="F1025" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1025" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1025" t="s">
         <v>9712</v>
       </c>
-      <c r="F1025" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1025" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1025" t="s">
+      <c r="I1025" t="s">
         <v>9713</v>
-      </c>
-      <c r="I1025" t="s">
-        <v>9714</v>
       </c>
     </row>
     <row r="1026" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1026" t="s">
+        <v>9714</v>
+      </c>
+      <c r="B1026" t="s">
         <v>9715</v>
       </c>
-      <c r="B1026" t="s">
+      <c r="C1026" t="s">
         <v>9716</v>
       </c>
-      <c r="C1026" t="s">
+      <c r="D1026" t="s">
         <v>9717</v>
       </c>
-      <c r="D1026" t="s">
+      <c r="E1026" t="s">
         <v>9718</v>
       </c>
-      <c r="E1026" t="s">
+      <c r="F1026" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1026" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1026" t="s">
         <v>9719</v>
       </c>
-      <c r="F1026" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1026" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1026" t="s">
+      <c r="I1026" t="s">
         <v>9720</v>
-      </c>
-      <c r="I1026" t="s">
-        <v>9721</v>
       </c>
     </row>
     <row r="1027" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1027" t="s">
+        <v>9721</v>
+      </c>
+      <c r="B1027" t="s">
         <v>9722</v>
       </c>
-      <c r="B1027" t="s">
+      <c r="C1027" t="s">
         <v>9723</v>
       </c>
-      <c r="C1027" t="s">
+      <c r="D1027" t="s">
         <v>9724</v>
       </c>
-      <c r="D1027" t="s">
+      <c r="E1027" t="s">
         <v>9725</v>
       </c>
-      <c r="E1027" t="s">
+      <c r="F1027" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1027" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1027" t="s">
         <v>9726</v>
       </c>
-      <c r="F1027" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1027" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1027" t="s">
+      <c r="I1027" t="s">
         <v>9727</v>
-      </c>
-      <c r="I1027" t="s">
-        <v>9728</v>
       </c>
     </row>
     <row r="1028" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1028" t="s">
+        <v>9728</v>
+      </c>
+      <c r="B1028" t="s">
         <v>9729</v>
       </c>
-      <c r="B1028" t="s">
+      <c r="C1028" t="s">
         <v>9730</v>
       </c>
-      <c r="C1028" t="s">
+      <c r="D1028" t="s">
         <v>9731</v>
       </c>
-      <c r="D1028" t="s">
+      <c r="E1028" t="s">
         <v>9732</v>
       </c>
-      <c r="E1028" t="s">
+      <c r="F1028" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1028" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1028" t="s">
         <v>9733</v>
       </c>
-      <c r="F1028" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1028" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1028" t="s">
+      <c r="I1028" t="s">
         <v>9734</v>
-      </c>
-      <c r="I1028" t="s">
-        <v>9735</v>
       </c>
     </row>
     <row r="1029" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1029" t="s">
+        <v>9735</v>
+      </c>
+      <c r="B1029" t="s">
         <v>9736</v>
       </c>
-      <c r="B1029" t="s">
+      <c r="C1029" t="s">
         <v>9737</v>
       </c>
-      <c r="C1029" t="s">
+      <c r="D1029" t="s">
         <v>9738</v>
       </c>
-      <c r="D1029" t="s">
+      <c r="E1029" t="s">
         <v>9739</v>
       </c>
-      <c r="E1029" t="s">
+      <c r="F1029" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1029" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1029" t="s">
         <v>9740</v>
       </c>
-      <c r="F1029" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1029" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1029" t="s">
+      <c r="I1029" t="s">
         <v>9741</v>
-      </c>
-      <c r="I1029" t="s">
-        <v>9742</v>
       </c>
     </row>
     <row r="1030" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1030" t="s">
+        <v>9742</v>
+      </c>
+      <c r="B1030" t="s">
         <v>9743</v>
       </c>
-      <c r="B1030" t="s">
+      <c r="C1030" t="s">
         <v>9744</v>
       </c>
-      <c r="C1030" t="s">
+      <c r="D1030" t="s">
         <v>9745</v>
       </c>
-      <c r="D1030" t="s">
+      <c r="E1030" t="s">
         <v>9746</v>
       </c>
-      <c r="E1030" t="s">
+      <c r="F1030" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1030" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1030" t="s">
         <v>9747</v>
       </c>
-      <c r="F1030" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1030" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1030" t="s">
+      <c r="I1030" t="s">
         <v>9748</v>
-      </c>
-      <c r="I1030" t="s">
-        <v>9749</v>
       </c>
     </row>
     <row r="1031" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1031" t="s">
+        <v>9749</v>
+      </c>
+      <c r="B1031" t="s">
         <v>9750</v>
       </c>
-      <c r="B1031" t="s">
+      <c r="C1031" t="s">
         <v>9751</v>
       </c>
-      <c r="C1031" t="s">
+      <c r="D1031" t="s">
         <v>9752</v>
       </c>
-      <c r="D1031" t="s">
+      <c r="E1031" t="s">
         <v>9753</v>
       </c>
-      <c r="E1031" t="s">
+      <c r="F1031" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1031" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1031" t="s">
         <v>9754</v>
       </c>
-      <c r="F1031" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1031" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1031" t="s">
+      <c r="I1031" t="s">
         <v>9755</v>
-      </c>
-      <c r="I1031" t="s">
-        <v>9756</v>
       </c>
     </row>
     <row r="1032" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1032" t="s">
+        <v>9756</v>
+      </c>
+      <c r="B1032" t="s">
         <v>9757</v>
       </c>
-      <c r="B1032" t="s">
+      <c r="C1032" t="s">
         <v>9758</v>
       </c>
-      <c r="C1032" t="s">
+      <c r="D1032" t="s">
         <v>9759</v>
       </c>
-      <c r="D1032" t="s">
+      <c r="E1032" t="s">
         <v>9760</v>
       </c>
-      <c r="E1032" t="s">
+      <c r="F1032" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1032" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1032" t="s">
         <v>9761</v>
       </c>
-      <c r="F1032" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1032" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1032" t="s">
+      <c r="I1032" t="s">
         <v>9762</v>
-      </c>
-      <c r="I1032" t="s">
-        <v>9763</v>
       </c>
     </row>
     <row r="1033" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1033" t="s">
+        <v>9763</v>
+      </c>
+      <c r="B1033" t="s">
         <v>9764</v>
       </c>
-      <c r="B1033" t="s">
+      <c r="C1033" t="s">
         <v>9765</v>
       </c>
-      <c r="C1033" t="s">
+      <c r="D1033" t="s">
         <v>9766</v>
       </c>
-      <c r="D1033" t="s">
+      <c r="E1033" t="s">
         <v>9767</v>
       </c>
-      <c r="E1033" t="s">
+      <c r="F1033" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1033" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1033" t="s">
         <v>9768</v>
       </c>
-      <c r="F1033" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1033" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1033" t="s">
+      <c r="I1033" t="s">
         <v>9769</v>
-      </c>
-      <c r="I1033" t="s">
-        <v>9770</v>
       </c>
     </row>
     <row r="1034" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1034" t="s">
+        <v>9770</v>
+      </c>
+      <c r="B1034" t="s">
         <v>9771</v>
       </c>
-      <c r="B1034" t="s">
+      <c r="C1034" t="s">
         <v>9772</v>
       </c>
-      <c r="C1034" t="s">
+      <c r="D1034" t="s">
         <v>9773</v>
       </c>
-      <c r="D1034" t="s">
+      <c r="E1034" t="s">
         <v>9774</v>
       </c>
-      <c r="E1034" t="s">
+      <c r="F1034" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1034" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1034" t="s">
         <v>9775</v>
       </c>
-      <c r="F1034" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1034" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1034" t="s">
+      <c r="I1034" t="s">
         <v>9776</v>
-      </c>
-      <c r="I1034" t="s">
-        <v>9777</v>
       </c>
     </row>
     <row r="1035" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1035" t="s">
+        <v>9777</v>
+      </c>
+      <c r="B1035" t="s">
         <v>9778</v>
       </c>
-      <c r="B1035" t="s">
+      <c r="C1035" t="s">
         <v>9779</v>
       </c>
-      <c r="C1035" t="s">
+      <c r="D1035" t="s">
         <v>9780</v>
       </c>
-      <c r="D1035" t="s">
+      <c r="E1035" t="s">
         <v>9781</v>
       </c>
-      <c r="E1035" t="s">
+      <c r="F1035" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1035" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1035" t="s">
         <v>9782</v>
       </c>
-      <c r="F1035" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1035" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1035" t="s">
+      <c r="I1035" t="s">
         <v>9783</v>
-      </c>
-      <c r="I1035" t="s">
-        <v>9784</v>
       </c>
     </row>
     <row r="1036" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1036" t="s">
+        <v>9784</v>
+      </c>
+      <c r="B1036" t="s">
         <v>9785</v>
       </c>
-      <c r="B1036" t="s">
+      <c r="C1036" t="s">
         <v>9786</v>
       </c>
-      <c r="C1036" t="s">
+      <c r="D1036" t="s">
         <v>9787</v>
       </c>
-      <c r="D1036" t="s">
+      <c r="E1036" t="s">
         <v>9788</v>
       </c>
-      <c r="E1036" t="s">
+      <c r="F1036" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1036" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1036" t="s">
+        <v>9775</v>
+      </c>
+      <c r="I1036" t="s">
         <v>9789</v>
-      </c>
-      <c r="F1036" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1036" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1036" t="s">
-        <v>9776</v>
-      </c>
-      <c r="I1036" t="s">
-        <v>9790</v>
       </c>
     </row>
     <row r="1037" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1037" t="s">
+        <v>9790</v>
+      </c>
+      <c r="B1037" t="s">
         <v>9791</v>
       </c>
-      <c r="B1037" t="s">
+      <c r="C1037" t="s">
         <v>9792</v>
       </c>
-      <c r="C1037" t="s">
+      <c r="D1037" t="s">
         <v>9793</v>
       </c>
-      <c r="D1037" t="s">
+      <c r="E1037" t="s">
         <v>9794</v>
       </c>
-      <c r="E1037" t="s">
+      <c r="F1037" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1037" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1037" t="s">
         <v>9795</v>
       </c>
-      <c r="F1037" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1037" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1037" t="s">
+      <c r="I1037" t="s">
         <v>9796</v>
-      </c>
-      <c r="I1037" t="s">
-        <v>9797</v>
       </c>
     </row>
     <row r="1038" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1038" t="s">
+        <v>9797</v>
+      </c>
+      <c r="B1038" t="s">
         <v>9798</v>
       </c>
-      <c r="B1038" t="s">
+      <c r="C1038" t="s">
         <v>9799</v>
       </c>
-      <c r="C1038" t="s">
+      <c r="D1038" t="s">
         <v>9800</v>
       </c>
-      <c r="D1038" t="s">
+      <c r="E1038" t="s">
         <v>9801</v>
       </c>
-      <c r="E1038" t="s">
+      <c r="F1038" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1038" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1038" t="s">
         <v>9802</v>
       </c>
-      <c r="F1038" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1038" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1038" t="s">
+      <c r="I1038" t="s">
         <v>9803</v>
-      </c>
-      <c r="I1038" t="s">
-        <v>9804</v>
       </c>
     </row>
     <row r="1039" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1039" t="s">
+        <v>9804</v>
+      </c>
+      <c r="B1039" t="s">
         <v>9805</v>
       </c>
-      <c r="B1039" t="s">
+      <c r="C1039" t="s">
         <v>9806</v>
       </c>
-      <c r="C1039" t="s">
+      <c r="D1039" t="s">
         <v>9807</v>
       </c>
-      <c r="D1039" t="s">
+      <c r="E1039" t="s">
         <v>9808</v>
       </c>
-      <c r="E1039" t="s">
+      <c r="F1039" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1039" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1039" t="s">
         <v>9809</v>
       </c>
-      <c r="F1039" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1039" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1039" t="s">
+      <c r="I1039" t="s">
         <v>9810</v>
-      </c>
-      <c r="I1039" t="s">
-        <v>9811</v>
       </c>
     </row>
     <row r="1040" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1040" t="s">
+        <v>9811</v>
+      </c>
+      <c r="B1040" t="s">
         <v>9812</v>
       </c>
-      <c r="B1040" t="s">
+      <c r="C1040" t="s">
         <v>9813</v>
       </c>
-      <c r="C1040" t="s">
+      <c r="D1040" t="s">
         <v>9814</v>
       </c>
-      <c r="D1040" t="s">
+      <c r="E1040" t="s">
         <v>9815</v>
       </c>
-      <c r="E1040" t="s">
+      <c r="F1040" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1040" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1040" t="s">
         <v>9816</v>
       </c>
-      <c r="F1040" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1040" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1040" t="s">
+      <c r="I1040" t="s">
         <v>9817</v>
-      </c>
-      <c r="I1040" t="s">
-        <v>9818</v>
       </c>
     </row>
     <row r="1041" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1041" t="s">
+        <v>9818</v>
+      </c>
+      <c r="B1041" t="s">
         <v>9819</v>
       </c>
-      <c r="B1041" t="s">
+      <c r="C1041" t="s">
         <v>9820</v>
       </c>
-      <c r="C1041" t="s">
+      <c r="D1041" t="s">
         <v>9821</v>
       </c>
-      <c r="D1041" t="s">
+      <c r="E1041" t="s">
         <v>9822</v>
       </c>
-      <c r="E1041" t="s">
+      <c r="F1041" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1041" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1041" t="s">
         <v>9823</v>
       </c>
-      <c r="F1041" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1041" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1041" t="s">
+      <c r="I1041" t="s">
         <v>9824</v>
-      </c>
-      <c r="I1041" t="s">
-        <v>9825</v>
       </c>
     </row>
     <row r="1042" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1042" t="s">
+        <v>9825</v>
+      </c>
+      <c r="B1042" t="s">
         <v>9826</v>
       </c>
-      <c r="B1042" t="s">
+      <c r="C1042" t="s">
         <v>9827</v>
       </c>
-      <c r="C1042" t="s">
+      <c r="D1042" t="s">
         <v>9828</v>
       </c>
-      <c r="D1042" t="s">
+      <c r="E1042" t="s">
         <v>9829</v>
       </c>
-      <c r="E1042" t="s">
+      <c r="F1042" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1042" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1042" t="s">
         <v>9830</v>
       </c>
-      <c r="F1042" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1042" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1042" t="s">
+      <c r="I1042" t="s">
         <v>9831</v>
-      </c>
-      <c r="I1042" t="s">
-        <v>9832</v>
       </c>
     </row>
     <row r="1043" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1043" t="s">
+        <v>9832</v>
+      </c>
+      <c r="B1043" t="s">
         <v>9833</v>
       </c>
-      <c r="B1043" t="s">
+      <c r="C1043" t="s">
         <v>9834</v>
       </c>
-      <c r="C1043" t="s">
+      <c r="D1043" t="s">
         <v>9835</v>
       </c>
-      <c r="D1043" t="s">
+      <c r="E1043" t="s">
         <v>9836</v>
       </c>
-      <c r="E1043" t="s">
+      <c r="F1043" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1043" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1043" t="s">
         <v>9837</v>
       </c>
-      <c r="F1043" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1043" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1043" t="s">
+      <c r="I1043" t="s">
         <v>9838</v>
-      </c>
-      <c r="I1043" t="s">
-        <v>9839</v>
       </c>
     </row>
     <row r="1044" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1044" t="s">
+        <v>9839</v>
+      </c>
+      <c r="B1044" t="s">
         <v>9840</v>
       </c>
-      <c r="B1044" t="s">
+      <c r="C1044" t="s">
         <v>9841</v>
       </c>
-      <c r="C1044" t="s">
+      <c r="D1044" t="s">
         <v>9842</v>
       </c>
-      <c r="D1044" t="s">
+      <c r="E1044" t="s">
         <v>9843</v>
       </c>
-      <c r="E1044" t="s">
+      <c r="F1044" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1044" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1044" t="s">
         <v>9844</v>
       </c>
-      <c r="F1044" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1044" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1044" t="s">
+      <c r="I1044" t="s">
         <v>9845</v>
-      </c>
-      <c r="I1044" t="s">
-        <v>9846</v>
       </c>
     </row>
     <row r="1045" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1045" t="s">
+        <v>9846</v>
+      </c>
+      <c r="B1045" t="s">
         <v>9847</v>
       </c>
-      <c r="B1045" t="s">
+      <c r="C1045" t="s">
         <v>9848</v>
       </c>
-      <c r="C1045" t="s">
+      <c r="D1045" t="s">
         <v>9849</v>
       </c>
-      <c r="D1045" t="s">
+      <c r="E1045" t="s">
         <v>9850</v>
       </c>
-      <c r="E1045" t="s">
+      <c r="F1045" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1045" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1045" t="s">
         <v>9851</v>
       </c>
-      <c r="F1045" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1045" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1045" t="s">
+      <c r="I1045" t="s">
         <v>9852</v>
-      </c>
-      <c r="I1045" t="s">
-        <v>9853</v>
       </c>
     </row>
     <row r="1046" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1046" t="s">
+        <v>9853</v>
+      </c>
+      <c r="B1046" t="s">
         <v>9854</v>
       </c>
-      <c r="B1046" t="s">
+      <c r="C1046" t="s">
         <v>9855</v>
       </c>
-      <c r="C1046" t="s">
+      <c r="D1046" t="s">
         <v>9856</v>
       </c>
-      <c r="D1046" t="s">
+      <c r="E1046" t="s">
         <v>9857</v>
       </c>
-      <c r="E1046" t="s">
+      <c r="F1046" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1046" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1046" t="s">
         <v>9858</v>
       </c>
-      <c r="F1046" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1046" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1046" t="s">
+      <c r="I1046" t="s">
         <v>9859</v>
-      </c>
-      <c r="I1046" t="s">
-        <v>9860</v>
       </c>
     </row>
     <row r="1047" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1047" t="s">
+        <v>9860</v>
+      </c>
+      <c r="B1047" t="s">
         <v>9861</v>
       </c>
-      <c r="B1047" t="s">
+      <c r="C1047" t="s">
         <v>9862</v>
       </c>
-      <c r="C1047" t="s">
+      <c r="D1047" t="s">
         <v>9863</v>
       </c>
-      <c r="D1047" t="s">
+      <c r="E1047" t="s">
         <v>9864</v>
       </c>
-      <c r="E1047" t="s">
+      <c r="F1047" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1047" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1047" t="s">
         <v>9865</v>
       </c>
-      <c r="F1047" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1047" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1047" t="s">
+      <c r="I1047" t="s">
         <v>9866</v>
-      </c>
-      <c r="I1047" t="s">
-        <v>9867</v>
       </c>
     </row>
     <row r="1048" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1048" t="s">
+        <v>9867</v>
+      </c>
+      <c r="B1048" t="s">
         <v>9868</v>
       </c>
-      <c r="B1048" t="s">
+      <c r="C1048" t="s">
         <v>9869</v>
       </c>
-      <c r="C1048" t="s">
+      <c r="D1048" t="s">
         <v>9870</v>
       </c>
-      <c r="D1048" t="s">
+      <c r="E1048" t="s">
         <v>9871</v>
       </c>
-      <c r="E1048" t="s">
+      <c r="F1048" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1048" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1048" t="s">
         <v>9872</v>
       </c>
-      <c r="F1048" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1048" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1048" t="s">
+      <c r="I1048" t="s">
         <v>9873</v>
-      </c>
-      <c r="I1048" t="s">
-        <v>9874</v>
       </c>
     </row>
     <row r="1049" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1049" t="s">
+        <v>9874</v>
+      </c>
+      <c r="B1049" t="s">
         <v>9875</v>
       </c>
-      <c r="B1049" t="s">
+      <c r="C1049" t="s">
         <v>9876</v>
       </c>
-      <c r="C1049" t="s">
+      <c r="D1049" t="s">
         <v>9877</v>
       </c>
-      <c r="D1049" t="s">
+      <c r="E1049" t="s">
         <v>9878</v>
       </c>
-      <c r="E1049" t="s">
+      <c r="F1049" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1049" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1049" t="s">
         <v>9879</v>
       </c>
-      <c r="F1049" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1049" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1049" t="s">
+      <c r="I1049" t="s">
         <v>9880</v>
-      </c>
-      <c r="I1049" t="s">
-        <v>9881</v>
       </c>
     </row>
     <row r="1050" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1050" t="s">
+        <v>9881</v>
+      </c>
+      <c r="B1050" t="s">
         <v>9882</v>
       </c>
-      <c r="B1050" t="s">
+      <c r="C1050" t="s">
         <v>9883</v>
       </c>
-      <c r="C1050" t="s">
+      <c r="D1050" t="s">
         <v>9884</v>
       </c>
-      <c r="D1050" t="s">
+      <c r="E1050" t="s">
         <v>9885</v>
       </c>
-      <c r="E1050" t="s">
+      <c r="F1050" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1050" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1050" t="s">
         <v>9886</v>
       </c>
-      <c r="F1050" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1050" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1050" t="s">
+      <c r="I1050" t="s">
         <v>9887</v>
-      </c>
-      <c r="I1050" t="s">
-        <v>9888</v>
       </c>
     </row>
     <row r="1051" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1051" t="s">
+        <v>9888</v>
+      </c>
+      <c r="B1051" t="s">
         <v>9889</v>
       </c>
-      <c r="B1051" t="s">
+      <c r="C1051" t="s">
         <v>9890</v>
       </c>
-      <c r="C1051" t="s">
+      <c r="D1051" t="s">
         <v>9891</v>
       </c>
-      <c r="D1051" t="s">
+      <c r="E1051" t="s">
         <v>9892</v>
       </c>
-      <c r="E1051" t="s">
+      <c r="F1051" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1051" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1051" t="s">
         <v>9893</v>
       </c>
-      <c r="F1051" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1051" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1051" t="s">
+      <c r="I1051" t="s">
         <v>9894</v>
-      </c>
-      <c r="I1051" t="s">
-        <v>9895</v>
       </c>
     </row>
     <row r="1052" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1052" t="s">
+        <v>9895</v>
+      </c>
+      <c r="B1052" t="s">
         <v>9896</v>
       </c>
-      <c r="B1052" t="s">
+      <c r="C1052" t="s">
         <v>9897</v>
       </c>
-      <c r="C1052" t="s">
+      <c r="D1052" t="s">
         <v>9898</v>
       </c>
-      <c r="D1052" t="s">
+      <c r="E1052" t="s">
         <v>9899</v>
       </c>
-      <c r="E1052" t="s">
+      <c r="F1052" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1052" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1052" t="s">
         <v>9900</v>
       </c>
-      <c r="F1052" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1052" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1052" t="s">
+      <c r="I1052" t="s">
         <v>9901</v>
-      </c>
-      <c r="I1052" t="s">
-        <v>9902</v>
       </c>
     </row>
     <row r="1053" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1053" t="s">
+        <v>9902</v>
+      </c>
+      <c r="B1053" t="s">
         <v>9903</v>
       </c>
-      <c r="B1053" t="s">
+      <c r="C1053" t="s">
         <v>9904</v>
       </c>
-      <c r="C1053" t="s">
+      <c r="D1053" t="s">
         <v>9905</v>
       </c>
-      <c r="D1053" t="s">
+      <c r="E1053" t="s">
         <v>9906</v>
       </c>
-      <c r="E1053" t="s">
+      <c r="F1053" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1053" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1053" t="s">
         <v>9907</v>
       </c>
-      <c r="F1053" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1053" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1053" t="s">
+      <c r="I1053" t="s">
         <v>9908</v>
-      </c>
-      <c r="I1053" t="s">
-        <v>9909</v>
       </c>
     </row>
     <row r="1054" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1054" t="s">
+        <v>9909</v>
+      </c>
+      <c r="B1054" t="s">
         <v>9910</v>
       </c>
-      <c r="B1054" t="s">
+      <c r="C1054" t="s">
         <v>9911</v>
       </c>
-      <c r="C1054" t="s">
+      <c r="D1054" t="s">
         <v>9912</v>
       </c>
-      <c r="D1054" t="s">
+      <c r="E1054" t="s">
         <v>9913</v>
       </c>
-      <c r="E1054" t="s">
+      <c r="F1054" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1054" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1054" t="s">
         <v>9914</v>
       </c>
-      <c r="F1054" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1054" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1054" t="s">
+      <c r="I1054" t="s">
         <v>9915</v>
-      </c>
-      <c r="I1054" t="s">
-        <v>9916</v>
       </c>
     </row>
     <row r="1055" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1055" t="s">
+        <v>9916</v>
+      </c>
+      <c r="B1055" t="s">
         <v>9917</v>
       </c>
-      <c r="B1055" t="s">
+      <c r="C1055" t="s">
         <v>9918</v>
       </c>
-      <c r="C1055" t="s">
+      <c r="D1055" t="s">
         <v>9919</v>
       </c>
-      <c r="D1055" t="s">
+      <c r="E1055" t="s">
         <v>9920</v>
       </c>
-      <c r="E1055" t="s">
+      <c r="F1055" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1055" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1055" t="s">
         <v>9921</v>
-      </c>
-      <c r="F1055" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1055" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1055" t="s">
-        <v>9922</v>
       </c>
     </row>
     <row r="1056" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1056" t="s">
+        <v>9922</v>
+      </c>
+      <c r="B1056" t="s">
         <v>9923</v>
       </c>
-      <c r="B1056" t="s">
+      <c r="C1056" t="s">
         <v>9924</v>
       </c>
-      <c r="C1056" t="s">
+      <c r="D1056" t="s">
         <v>9925</v>
       </c>
-      <c r="D1056" t="s">
+      <c r="E1056" t="s">
         <v>9926</v>
       </c>
-      <c r="E1056" t="s">
+      <c r="F1056" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1056" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1056" t="s">
         <v>9927</v>
-      </c>
-      <c r="F1056" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1056" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1056" t="s">
-        <v>9928</v>
       </c>
     </row>
     <row r="1057" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1057" t="s">
-        <v>9929</v>
+        <v>9928</v>
       </c>
       <c r="B1057" t="s">
         <v>3674</v>
       </c>
       <c r="C1057" t="s">
+        <v>9929</v>
+      </c>
+      <c r="D1057" t="s">
         <v>9930</v>
       </c>
-      <c r="D1057" t="s">
+      <c r="E1057" t="s">
         <v>9931</v>
       </c>
-      <c r="E1057" t="s">
+      <c r="F1057" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1057" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1057" t="s">
         <v>9932</v>
       </c>
-      <c r="F1057" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1057" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1057" t="s">
+      <c r="I1057" t="s">
         <v>9933</v>
-      </c>
-      <c r="I1057" t="s">
-        <v>9934</v>
       </c>
     </row>
     <row r="1058" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1058" t="s">
+        <v>9934</v>
+      </c>
+      <c r="B1058" t="s">
         <v>9935</v>
       </c>
-      <c r="B1058" t="s">
+      <c r="C1058" t="s">
         <v>9936</v>
       </c>
-      <c r="C1058" t="s">
+      <c r="D1058" t="s">
         <v>9937</v>
       </c>
-      <c r="D1058" t="s">
+      <c r="E1058" t="s">
         <v>9938</v>
-      </c>
-      <c r="E1058" t="s">
-        <v>9939</v>
       </c>
       <c r="F1058" t="s">
         <v>5496</v>
@@ -60134,79 +60131,79 @@
         <v>6179</v>
       </c>
       <c r="I1058" t="s">
-        <v>9940</v>
+        <v>9939</v>
       </c>
     </row>
     <row r="1059" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1059" t="s">
+        <v>9940</v>
+      </c>
+      <c r="B1059" t="s">
         <v>9941</v>
       </c>
-      <c r="B1059" t="s">
+      <c r="C1059" t="s">
         <v>9942</v>
       </c>
-      <c r="C1059" t="s">
+      <c r="D1059" t="s">
         <v>9943</v>
       </c>
-      <c r="D1059" t="s">
+      <c r="E1059" t="s">
         <v>9944</v>
       </c>
-      <c r="E1059" t="s">
+      <c r="F1059" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1059" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1059" t="s">
         <v>9945</v>
       </c>
-      <c r="F1059" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1059" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1059" t="s">
+      <c r="I1059" t="s">
         <v>9946</v>
-      </c>
-      <c r="I1059" t="s">
-        <v>9947</v>
       </c>
     </row>
     <row r="1060" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1060" t="s">
+        <v>9947</v>
+      </c>
+      <c r="B1060" t="s">
         <v>9948</v>
       </c>
-      <c r="B1060" t="s">
+      <c r="C1060" t="s">
         <v>9949</v>
       </c>
-      <c r="C1060" t="s">
+      <c r="D1060" t="s">
         <v>9950</v>
       </c>
-      <c r="D1060" t="s">
+      <c r="E1060" t="s">
         <v>9951</v>
       </c>
-      <c r="E1060" t="s">
+      <c r="F1060" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1060" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1060" t="s">
         <v>9952</v>
-      </c>
-      <c r="F1060" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1060" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1060" t="s">
-        <v>9953</v>
       </c>
     </row>
     <row r="1061" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1061" t="s">
+        <v>9953</v>
+      </c>
+      <c r="B1061" t="s">
         <v>9954</v>
       </c>
-      <c r="B1061" t="s">
+      <c r="C1061" t="s">
         <v>9955</v>
       </c>
-      <c r="C1061" t="s">
+      <c r="D1061" t="s">
         <v>9956</v>
       </c>
-      <c r="D1061" t="s">
+      <c r="E1061" t="s">
         <v>9957</v>
-      </c>
-      <c r="E1061" t="s">
-        <v>9958</v>
       </c>
       <c r="F1061" t="s">
         <v>5496</v>
@@ -60218,108 +60215,108 @@
         <v>5714</v>
       </c>
       <c r="I1061" t="s">
-        <v>9959</v>
+        <v>9958</v>
       </c>
     </row>
     <row r="1062" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1062" t="s">
+        <v>9959</v>
+      </c>
+      <c r="B1062" t="s">
         <v>9960</v>
       </c>
-      <c r="B1062" t="s">
+      <c r="C1062" t="s">
         <v>9961</v>
       </c>
-      <c r="C1062" t="s">
+      <c r="D1062" t="s">
         <v>9962</v>
       </c>
-      <c r="D1062" t="s">
+      <c r="E1062" t="s">
         <v>9963</v>
       </c>
-      <c r="E1062" t="s">
+      <c r="F1062" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1062" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1062" t="s">
         <v>9964</v>
       </c>
-      <c r="F1062" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1062" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1062" t="s">
+      <c r="I1062" t="s">
         <v>9965</v>
-      </c>
-      <c r="I1062" t="s">
-        <v>9966</v>
       </c>
     </row>
     <row r="1063" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1063" t="s">
+        <v>9966</v>
+      </c>
+      <c r="B1063" t="s">
         <v>9967</v>
       </c>
-      <c r="B1063" t="s">
+      <c r="C1063" t="s">
         <v>9968</v>
       </c>
-      <c r="C1063" t="s">
+      <c r="D1063" t="s">
         <v>9969</v>
       </c>
-      <c r="D1063" t="s">
+      <c r="E1063" t="s">
         <v>9970</v>
       </c>
-      <c r="E1063" t="s">
+      <c r="F1063" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1063" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1063" t="s">
         <v>9971</v>
       </c>
-      <c r="F1063" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1063" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1063" t="s">
+      <c r="I1063" t="s">
         <v>9972</v>
-      </c>
-      <c r="I1063" t="s">
-        <v>9973</v>
       </c>
     </row>
     <row r="1064" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1064" t="s">
+        <v>9973</v>
+      </c>
+      <c r="B1064" t="s">
         <v>9974</v>
       </c>
-      <c r="B1064" t="s">
+      <c r="C1064" t="s">
         <v>9975</v>
       </c>
-      <c r="C1064" t="s">
+      <c r="D1064" t="s">
         <v>9976</v>
       </c>
-      <c r="D1064" t="s">
+      <c r="E1064" t="s">
         <v>9977</v>
       </c>
-      <c r="E1064" t="s">
+      <c r="F1064" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1064" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1064" t="s">
         <v>9978</v>
-      </c>
-      <c r="F1064" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1064" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1064" t="s">
-        <v>9979</v>
       </c>
     </row>
     <row r="1065" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1065" t="s">
+        <v>9979</v>
+      </c>
+      <c r="B1065" t="s">
         <v>9980</v>
       </c>
-      <c r="B1065" t="s">
+      <c r="C1065" t="s">
         <v>9981</v>
       </c>
-      <c r="C1065" t="s">
+      <c r="D1065" t="s">
         <v>9982</v>
       </c>
-      <c r="D1065" t="s">
+      <c r="E1065" t="s">
         <v>9983</v>
-      </c>
-      <c r="E1065" t="s">
-        <v>9984</v>
       </c>
       <c r="F1065" t="s">
         <v>5496</v>
@@ -60333,48 +60330,48 @@
     </row>
     <row r="1066" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1066" t="s">
+        <v>9984</v>
+      </c>
+      <c r="B1066" t="s">
         <v>9985</v>
       </c>
-      <c r="B1066" t="s">
+      <c r="C1066" t="s">
         <v>9986</v>
       </c>
-      <c r="C1066" t="s">
+      <c r="D1066" t="s">
         <v>9987</v>
       </c>
-      <c r="D1066" t="s">
+      <c r="E1066" t="s">
         <v>9988</v>
       </c>
-      <c r="E1066" t="s">
+      <c r="F1066" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1066" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1066" t="s">
+        <v>9370</v>
+      </c>
+      <c r="I1066" t="s">
         <v>9989</v>
-      </c>
-      <c r="F1066" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1066" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1066" t="s">
-        <v>9371</v>
-      </c>
-      <c r="I1066" t="s">
-        <v>9990</v>
       </c>
     </row>
     <row r="1067" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1067" t="s">
+        <v>9990</v>
+      </c>
+      <c r="B1067" t="s">
         <v>9991</v>
       </c>
-      <c r="B1067" t="s">
+      <c r="C1067" t="s">
         <v>9992</v>
       </c>
-      <c r="C1067" t="s">
+      <c r="D1067" t="s">
         <v>9993</v>
       </c>
-      <c r="D1067" t="s">
+      <c r="E1067" t="s">
         <v>9994</v>
-      </c>
-      <c r="E1067" t="s">
-        <v>9995</v>
       </c>
       <c r="F1067" t="s">
         <v>5496</v>
@@ -60386,82 +60383,82 @@
         <v>6582</v>
       </c>
       <c r="I1067" t="s">
-        <v>9996</v>
+        <v>9995</v>
       </c>
     </row>
     <row r="1068" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1068" t="s">
+        <v>9996</v>
+      </c>
+      <c r="B1068" t="s">
         <v>9997</v>
       </c>
-      <c r="B1068" t="s">
+      <c r="C1068" t="s">
         <v>9998</v>
       </c>
-      <c r="C1068" t="s">
+      <c r="D1068" t="s">
         <v>9999</v>
       </c>
-      <c r="D1068" t="s">
+      <c r="E1068" t="s">
         <v>10000</v>
       </c>
-      <c r="E1068" t="s">
+      <c r="F1068" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1068" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1068" t="s">
         <v>10001</v>
       </c>
-      <c r="F1068" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1068" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1068" t="s">
+      <c r="I1068" t="s">
         <v>10002</v>
-      </c>
-      <c r="I1068" t="s">
-        <v>10003</v>
       </c>
     </row>
     <row r="1069" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1069" t="s">
+        <v>10003</v>
+      </c>
+      <c r="B1069" t="s">
         <v>10004</v>
       </c>
-      <c r="B1069" t="s">
+      <c r="C1069" t="s">
         <v>10005</v>
       </c>
-      <c r="C1069" t="s">
+      <c r="D1069" t="s">
         <v>10006</v>
       </c>
-      <c r="D1069" t="s">
+      <c r="E1069" t="s">
         <v>10007</v>
       </c>
-      <c r="E1069" t="s">
+      <c r="F1069" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1069" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1069" t="s">
         <v>10008</v>
       </c>
-      <c r="F1069" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1069" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1069" t="s">
+      <c r="I1069" t="s">
         <v>10009</v>
-      </c>
-      <c r="I1069" t="s">
-        <v>10010</v>
       </c>
     </row>
     <row r="1070" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1070" t="s">
+        <v>10010</v>
+      </c>
+      <c r="B1070" t="s">
         <v>10011</v>
       </c>
-      <c r="B1070" t="s">
+      <c r="C1070" t="s">
         <v>10012</v>
       </c>
-      <c r="C1070" t="s">
+      <c r="D1070" t="s">
         <v>10013</v>
       </c>
-      <c r="D1070" t="s">
+      <c r="E1070" t="s">
         <v>10014</v>
-      </c>
-      <c r="E1070" t="s">
-        <v>10015</v>
       </c>
       <c r="F1070" t="s">
         <v>5496</v>
@@ -60475,77 +60472,77 @@
     </row>
     <row r="1071" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1071" t="s">
+        <v>10015</v>
+      </c>
+      <c r="B1071" t="s">
         <v>10016</v>
       </c>
-      <c r="B1071" t="s">
+      <c r="C1071" t="s">
         <v>10017</v>
       </c>
-      <c r="C1071" t="s">
+      <c r="D1071" t="s">
         <v>10018</v>
       </c>
-      <c r="D1071" t="s">
+      <c r="E1071" t="s">
         <v>10019</v>
       </c>
-      <c r="E1071" t="s">
+      <c r="F1071" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1071" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1071" t="s">
         <v>10020</v>
       </c>
-      <c r="F1071" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1071" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1071" t="s">
+      <c r="I1071" t="s">
         <v>10021</v>
-      </c>
-      <c r="I1071" t="s">
-        <v>10022</v>
       </c>
     </row>
     <row r="1072" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1072" t="s">
+        <v>10022</v>
+      </c>
+      <c r="B1072" t="s">
         <v>10023</v>
       </c>
-      <c r="B1072" t="s">
+      <c r="C1072" t="s">
         <v>10024</v>
       </c>
-      <c r="C1072" t="s">
+      <c r="D1072" t="s">
         <v>10025</v>
       </c>
-      <c r="D1072" t="s">
+      <c r="E1072" t="s">
         <v>10026</v>
       </c>
-      <c r="E1072" t="s">
+      <c r="F1072" t="s">
+        <v>5496</v>
+      </c>
+      <c r="G1072" t="s">
+        <v>5496</v>
+      </c>
+      <c r="H1072" t="s">
         <v>10027</v>
       </c>
-      <c r="F1072" t="s">
-        <v>5496</v>
-      </c>
-      <c r="G1072" t="s">
-        <v>5496</v>
-      </c>
-      <c r="H1072" t="s">
+      <c r="I1072" t="s">
         <v>10028</v>
-      </c>
-      <c r="I1072" t="s">
-        <v>10029</v>
       </c>
     </row>
     <row r="1073" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1073" t="s">
+        <v>10029</v>
+      </c>
+      <c r="B1073" t="s">
         <v>10030</v>
       </c>
-      <c r="B1073" t="s">
+      <c r="C1073" t="s">
         <v>10031</v>
       </c>
-      <c r="C1073" t="s">
+      <c r="D1073" t="s">
         <v>10032</v>
       </c>
-      <c r="D1073" t="s">
+      <c r="E1073" t="s">
         <v>10033</v>
-      </c>
-      <c r="E1073" t="s">
-        <v>10034</v>
       </c>
       <c r="F1073" t="s">
         <v>5496</v>
@@ -60557,7 +60554,7 @@
         <v>6458</v>
       </c>
       <c r="I1073" t="s">
-        <v>10035</v>
+        <v>10034</v>
       </c>
     </row>
     <row r="1074" spans="1:9" x14ac:dyDescent="0.3">
